--- a/1_apps/linux/sjudas/confinamento_batidas_trendline/dados_processados.xlsx
+++ b/1_apps/linux/sjudas/confinamento_batidas_trendline/dados_processados.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4188,6 +4188,4502 @@
         <v>3.89</v>
       </c>
     </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>29898</v>
+      </c>
+      <c r="B467" s="3" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>29899</v>
+      </c>
+      <c r="B468" s="3" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>29900</v>
+      </c>
+      <c r="B469" s="3" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>29901</v>
+      </c>
+      <c r="B470" s="3" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>29902</v>
+      </c>
+      <c r="B471" s="3" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>29903</v>
+      </c>
+      <c r="B472" s="3" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>29904</v>
+      </c>
+      <c r="B473" s="5" t="n">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>29905</v>
+      </c>
+      <c r="B474" s="3" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>29906</v>
+      </c>
+      <c r="B475" s="2" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>29907</v>
+      </c>
+      <c r="B476" s="3" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>29908</v>
+      </c>
+      <c r="B477" s="3" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>29909</v>
+      </c>
+      <c r="B478" s="5" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>29910</v>
+      </c>
+      <c r="B479" s="3" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>29911</v>
+      </c>
+      <c r="B480" s="5" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>29912</v>
+      </c>
+      <c r="B481" s="4" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>29913</v>
+      </c>
+      <c r="B482" s="3" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>29914</v>
+      </c>
+      <c r="B483" s="3" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>29915</v>
+      </c>
+      <c r="B484" s="2" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>29916</v>
+      </c>
+      <c r="B485" s="3" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>29917</v>
+      </c>
+      <c r="B486" s="3" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>29918</v>
+      </c>
+      <c r="B487" s="3" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>29919</v>
+      </c>
+      <c r="B488" s="3" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>29920</v>
+      </c>
+      <c r="B489" s="3" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>29921</v>
+      </c>
+      <c r="B490" s="3" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>29922</v>
+      </c>
+      <c r="B491" s="3" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>29923</v>
+      </c>
+      <c r="B492" s="3" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>29924</v>
+      </c>
+      <c r="B493" s="3" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>29925</v>
+      </c>
+      <c r="B494" s="3" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>29926</v>
+      </c>
+      <c r="B495" s="4" t="n">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>29927</v>
+      </c>
+      <c r="B496" s="5" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>29928</v>
+      </c>
+      <c r="B497" s="3" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>29929</v>
+      </c>
+      <c r="B498" s="3" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>29930</v>
+      </c>
+      <c r="B499" s="2" t="n">
+        <v>12.07</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>29931</v>
+      </c>
+      <c r="B500" s="4" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>29932</v>
+      </c>
+      <c r="B501" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>29933</v>
+      </c>
+      <c r="B502" s="3" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>29934</v>
+      </c>
+      <c r="B503" s="3" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>29935</v>
+      </c>
+      <c r="B504" s="3" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>29936</v>
+      </c>
+      <c r="B505" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>29937</v>
+      </c>
+      <c r="B506" s="3" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>29938</v>
+      </c>
+      <c r="B507" s="5" t="n">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>29939</v>
+      </c>
+      <c r="B508" s="4" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>29940</v>
+      </c>
+      <c r="B509" s="5" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>29941</v>
+      </c>
+      <c r="B510" s="2" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>29942</v>
+      </c>
+      <c r="B511" s="3" t="n">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>29943</v>
+      </c>
+      <c r="B512" s="3" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>29944</v>
+      </c>
+      <c r="B513" s="5" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>29945</v>
+      </c>
+      <c r="B514" s="5" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>29946</v>
+      </c>
+      <c r="B515" s="3" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>29947</v>
+      </c>
+      <c r="B516" s="5" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>29948</v>
+      </c>
+      <c r="B517" s="5" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>29949</v>
+      </c>
+      <c r="B518" s="3" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>29950</v>
+      </c>
+      <c r="B519" s="2" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>29951</v>
+      </c>
+      <c r="B520" s="5" t="n">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>29952</v>
+      </c>
+      <c r="B521" s="3" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>29953</v>
+      </c>
+      <c r="B522" s="5" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>29954</v>
+      </c>
+      <c r="B523" s="4" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>29955</v>
+      </c>
+      <c r="B524" s="3" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>29956</v>
+      </c>
+      <c r="B525" s="3" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>29957</v>
+      </c>
+      <c r="B526" s="2" t="n">
+        <v>14.76</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>29958</v>
+      </c>
+      <c r="B527" s="5" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>29959</v>
+      </c>
+      <c r="B528" s="2" t="n">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>29960</v>
+      </c>
+      <c r="B529" s="5" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>29961</v>
+      </c>
+      <c r="B530" s="3" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>29962</v>
+      </c>
+      <c r="B531" s="5" t="n">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>29963</v>
+      </c>
+      <c r="B532" s="5" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>29964</v>
+      </c>
+      <c r="B533" s="4" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>29965</v>
+      </c>
+      <c r="B534" s="5" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>29966</v>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>19.69</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>29967</v>
+      </c>
+      <c r="B536" s="4" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>29968</v>
+      </c>
+      <c r="B537" s="4" t="n">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>29969</v>
+      </c>
+      <c r="B538" s="4" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>29970</v>
+      </c>
+      <c r="B539" s="5" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>29971</v>
+      </c>
+      <c r="B540" s="3" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>29972</v>
+      </c>
+      <c r="B541" s="2" t="n">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>29973</v>
+      </c>
+      <c r="B542" s="3" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>29974</v>
+      </c>
+      <c r="B543" s="4" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>29975</v>
+      </c>
+      <c r="B544" s="5" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>29976</v>
+      </c>
+      <c r="B545" s="5" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>29977</v>
+      </c>
+      <c r="B546" s="5" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>29978</v>
+      </c>
+      <c r="B547" s="3" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>29979</v>
+      </c>
+      <c r="B548" s="2" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>29980</v>
+      </c>
+      <c r="B549" s="2" t="n">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>29981</v>
+      </c>
+      <c r="B550" s="5" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>29982</v>
+      </c>
+      <c r="B551" s="3" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>29983</v>
+      </c>
+      <c r="B552" s="4" t="n">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>29984</v>
+      </c>
+      <c r="B553" s="5" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>29985</v>
+      </c>
+      <c r="B554" s="3" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>29986</v>
+      </c>
+      <c r="B555" s="5" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>29987</v>
+      </c>
+      <c r="B556" s="2" t="n">
+        <v>15.36</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>29988</v>
+      </c>
+      <c r="B557" s="3" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>29989</v>
+      </c>
+      <c r="B558" s="3" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>29990</v>
+      </c>
+      <c r="B559" s="3" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>29991</v>
+      </c>
+      <c r="B560" s="2" t="n">
+        <v>32.04</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>29992</v>
+      </c>
+      <c r="B561" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>29993</v>
+      </c>
+      <c r="B562" s="3" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>29994</v>
+      </c>
+      <c r="B563" s="3" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>29995</v>
+      </c>
+      <c r="B564" s="2" t="n">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>29996</v>
+      </c>
+      <c r="B565" s="3" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>29997</v>
+      </c>
+      <c r="B566" s="5" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>29998</v>
+      </c>
+      <c r="B567" s="2" t="n">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>29999</v>
+      </c>
+      <c r="B568" s="4" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>30000</v>
+      </c>
+      <c r="B569" s="3" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>30001</v>
+      </c>
+      <c r="B570" s="3" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>30002</v>
+      </c>
+      <c r="B571" s="4" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B572" s="5" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>30004</v>
+      </c>
+      <c r="B573" s="5" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>30005</v>
+      </c>
+      <c r="B574" s="3" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>30006</v>
+      </c>
+      <c r="B575" s="3" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>30007</v>
+      </c>
+      <c r="B576" s="3" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>30008</v>
+      </c>
+      <c r="B577" s="3" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>30009</v>
+      </c>
+      <c r="B578" s="3" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>30010</v>
+      </c>
+      <c r="B579" s="4" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>30011</v>
+      </c>
+      <c r="B580" s="5" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>30012</v>
+      </c>
+      <c r="B581" s="2" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>30013</v>
+      </c>
+      <c r="B582" s="5" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>30014</v>
+      </c>
+      <c r="B583" s="4" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>30015</v>
+      </c>
+      <c r="B584" s="3" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>30016</v>
+      </c>
+      <c r="B585" s="4" t="n">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>30017</v>
+      </c>
+      <c r="B586" s="3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>30018</v>
+      </c>
+      <c r="B587" s="3" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>30019</v>
+      </c>
+      <c r="B588" s="4" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>30020</v>
+      </c>
+      <c r="B589" s="3" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>30021</v>
+      </c>
+      <c r="B590" s="4" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>30022</v>
+      </c>
+      <c r="B591" s="4" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>30023</v>
+      </c>
+      <c r="B592" s="2" t="n">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>30024</v>
+      </c>
+      <c r="B593" s="3" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>30025</v>
+      </c>
+      <c r="B594" s="3" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>30026</v>
+      </c>
+      <c r="B595" s="2" t="n">
+        <v>17.66</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>30027</v>
+      </c>
+      <c r="B596" s="5" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>30028</v>
+      </c>
+      <c r="B597" s="3" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>30029</v>
+      </c>
+      <c r="B598" s="2" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>30030</v>
+      </c>
+      <c r="B599" s="3" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>30031</v>
+      </c>
+      <c r="B600" s="2" t="n">
+        <v>11.53</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B601" s="3" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B602" s="3" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B603" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B604" s="3" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B605" s="4" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>30037</v>
+      </c>
+      <c r="B606" s="3" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>30038</v>
+      </c>
+      <c r="B607" s="3" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>30039</v>
+      </c>
+      <c r="B608" s="5" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>30040</v>
+      </c>
+      <c r="B609" s="3" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>30041</v>
+      </c>
+      <c r="B610" s="3" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>30042</v>
+      </c>
+      <c r="B611" s="3" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>30043</v>
+      </c>
+      <c r="B612" s="4" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>30044</v>
+      </c>
+      <c r="B613" s="3" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>30045</v>
+      </c>
+      <c r="B614" s="3" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>30046</v>
+      </c>
+      <c r="B615" s="5" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>30048</v>
+      </c>
+      <c r="B616" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>30049</v>
+      </c>
+      <c r="B617" s="3" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>30050</v>
+      </c>
+      <c r="B618" s="3" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>30051</v>
+      </c>
+      <c r="B619" s="4" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>30052</v>
+      </c>
+      <c r="B620" s="5" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>30053</v>
+      </c>
+      <c r="B621" s="5" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>30054</v>
+      </c>
+      <c r="B622" s="3" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>30055</v>
+      </c>
+      <c r="B623" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>30056</v>
+      </c>
+      <c r="B624" s="3" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>30057</v>
+      </c>
+      <c r="B625" s="3" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>30058</v>
+      </c>
+      <c r="B626" s="5" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>30059</v>
+      </c>
+      <c r="B627" s="5" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>30060</v>
+      </c>
+      <c r="B628" s="3" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>30061</v>
+      </c>
+      <c r="B629" s="5" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>30062</v>
+      </c>
+      <c r="B630" s="5" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>30063</v>
+      </c>
+      <c r="B631" s="3" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>30064</v>
+      </c>
+      <c r="B632" s="3" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>30065</v>
+      </c>
+      <c r="B633" s="5" t="n">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>30066</v>
+      </c>
+      <c r="B634" s="2" t="n">
+        <v>108.05</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>30067</v>
+      </c>
+      <c r="B635" s="3" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>30068</v>
+      </c>
+      <c r="B636" s="3" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>30069</v>
+      </c>
+      <c r="B637" s="3" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>30070</v>
+      </c>
+      <c r="B638" s="3" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>30071</v>
+      </c>
+      <c r="B639" s="3" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>30072</v>
+      </c>
+      <c r="B640" s="5" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>30073</v>
+      </c>
+      <c r="B641" s="4" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>30074</v>
+      </c>
+      <c r="B642" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>30075</v>
+      </c>
+      <c r="B643" s="2" t="n">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>30076</v>
+      </c>
+      <c r="B644" s="5" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>30077</v>
+      </c>
+      <c r="B645" s="3" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>30078</v>
+      </c>
+      <c r="B646" s="4" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>30079</v>
+      </c>
+      <c r="B647" s="5" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>30080</v>
+      </c>
+      <c r="B648" s="3" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>30081</v>
+      </c>
+      <c r="B649" s="5" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>30082</v>
+      </c>
+      <c r="B650" s="3" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>30083</v>
+      </c>
+      <c r="B651" s="5" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>30084</v>
+      </c>
+      <c r="B652" s="3" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>30085</v>
+      </c>
+      <c r="B653" s="3" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>30086</v>
+      </c>
+      <c r="B654" s="3" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>30087</v>
+      </c>
+      <c r="B655" s="3" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>30088</v>
+      </c>
+      <c r="B656" s="5" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>30089</v>
+      </c>
+      <c r="B657" s="3" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>30090</v>
+      </c>
+      <c r="B658" s="5" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>30091</v>
+      </c>
+      <c r="B659" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>30092</v>
+      </c>
+      <c r="B660" s="3" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>30093</v>
+      </c>
+      <c r="B661" s="5" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>30094</v>
+      </c>
+      <c r="B662" s="3" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>30095</v>
+      </c>
+      <c r="B663" s="5" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>30096</v>
+      </c>
+      <c r="B664" s="3" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>30097</v>
+      </c>
+      <c r="B665" s="4" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>30098</v>
+      </c>
+      <c r="B666" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>30099</v>
+      </c>
+      <c r="B667" s="3" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>30100</v>
+      </c>
+      <c r="B668" s="3" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>30101</v>
+      </c>
+      <c r="B669" s="5" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>30102</v>
+      </c>
+      <c r="B670" s="5" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>30103</v>
+      </c>
+      <c r="B671" s="5" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>30104</v>
+      </c>
+      <c r="B672" s="5" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>30105</v>
+      </c>
+      <c r="B673" s="5" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>30106</v>
+      </c>
+      <c r="B674" s="5" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>30107</v>
+      </c>
+      <c r="B675" s="2" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>30108</v>
+      </c>
+      <c r="B676" s="3" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>30109</v>
+      </c>
+      <c r="B677" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>30110</v>
+      </c>
+      <c r="B678" s="5" t="n">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>30111</v>
+      </c>
+      <c r="B679" s="3" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>30112</v>
+      </c>
+      <c r="B680" s="5" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>30113</v>
+      </c>
+      <c r="B681" s="3" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>30114</v>
+      </c>
+      <c r="B682" s="3" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>30115</v>
+      </c>
+      <c r="B683" s="2" t="n">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>30116</v>
+      </c>
+      <c r="B684" s="3" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>30117</v>
+      </c>
+      <c r="B685" s="3" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>30118</v>
+      </c>
+      <c r="B686" s="3" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>30119</v>
+      </c>
+      <c r="B687" s="3" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>30120</v>
+      </c>
+      <c r="B688" s="5" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>30121</v>
+      </c>
+      <c r="B689" s="3" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>30122</v>
+      </c>
+      <c r="B690" s="5" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>30123</v>
+      </c>
+      <c r="B691" s="5" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>30124</v>
+      </c>
+      <c r="B692" s="2" t="n">
+        <v>25.32</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>30125</v>
+      </c>
+      <c r="B693" s="2" t="n">
+        <v>9.460000000000001</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>30126</v>
+      </c>
+      <c r="B694" s="5" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>30127</v>
+      </c>
+      <c r="B695" s="5" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>30128</v>
+      </c>
+      <c r="B696" s="5" t="n">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>30129</v>
+      </c>
+      <c r="B697" s="3" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>30130</v>
+      </c>
+      <c r="B698" s="3" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>30131</v>
+      </c>
+      <c r="B699" s="3" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>30132</v>
+      </c>
+      <c r="B700" s="3" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>30133</v>
+      </c>
+      <c r="B701" s="4" t="n">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>30134</v>
+      </c>
+      <c r="B702" s="4" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>30135</v>
+      </c>
+      <c r="B703" s="3" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>30136</v>
+      </c>
+      <c r="B704" s="2" t="n">
+        <v>17.39</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>30137</v>
+      </c>
+      <c r="B705" s="3" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>30138</v>
+      </c>
+      <c r="B706" s="4" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>30139</v>
+      </c>
+      <c r="B707" s="2" t="n">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>30140</v>
+      </c>
+      <c r="B708" s="4" t="n">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>30141</v>
+      </c>
+      <c r="B709" s="3" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>30142</v>
+      </c>
+      <c r="B710" s="5" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>30143</v>
+      </c>
+      <c r="B711" s="2" t="n">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>30144</v>
+      </c>
+      <c r="B712" s="3" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>30145</v>
+      </c>
+      <c r="B713" s="5" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>30146</v>
+      </c>
+      <c r="B714" s="5" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>30147</v>
+      </c>
+      <c r="B715" s="5" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>30148</v>
+      </c>
+      <c r="B716" s="5" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>30149</v>
+      </c>
+      <c r="B717" s="3" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>30150</v>
+      </c>
+      <c r="B718" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>30151</v>
+      </c>
+      <c r="B719" s="3" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>30152</v>
+      </c>
+      <c r="B720" s="5" t="n">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>30153</v>
+      </c>
+      <c r="B721" s="2" t="n">
+        <v>11.02</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>30154</v>
+      </c>
+      <c r="B722" s="3" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>30155</v>
+      </c>
+      <c r="B723" s="5" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>30156</v>
+      </c>
+      <c r="B724" s="5" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>30157</v>
+      </c>
+      <c r="B725" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>30158</v>
+      </c>
+      <c r="B726" s="3" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>30159</v>
+      </c>
+      <c r="B727" s="3" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>30160</v>
+      </c>
+      <c r="B728" s="3" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>30161</v>
+      </c>
+      <c r="B729" s="3" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>30162</v>
+      </c>
+      <c r="B730" s="3" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>30163</v>
+      </c>
+      <c r="B731" s="5" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>30164</v>
+      </c>
+      <c r="B732" s="5" t="n">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>30165</v>
+      </c>
+      <c r="B733" s="5" t="n">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>30166</v>
+      </c>
+      <c r="B734" s="3" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>30167</v>
+      </c>
+      <c r="B735" s="5" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>30168</v>
+      </c>
+      <c r="B736" s="5" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>30169</v>
+      </c>
+      <c r="B737" s="5" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>30170</v>
+      </c>
+      <c r="B738" s="3" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>30171</v>
+      </c>
+      <c r="B739" s="4" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>30172</v>
+      </c>
+      <c r="B740" s="3" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>30173</v>
+      </c>
+      <c r="B741" s="5" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>30174</v>
+      </c>
+      <c r="B742" s="3" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>30175</v>
+      </c>
+      <c r="B743" s="5" t="n">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>30176</v>
+      </c>
+      <c r="B744" s="2" t="n">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>30177</v>
+      </c>
+      <c r="B745" s="3" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>30178</v>
+      </c>
+      <c r="B746" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>30179</v>
+      </c>
+      <c r="B747" s="3" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>30180</v>
+      </c>
+      <c r="B748" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>30181</v>
+      </c>
+      <c r="B749" s="2" t="n">
+        <v>8.970000000000001</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>30182</v>
+      </c>
+      <c r="B750" s="3" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>30183</v>
+      </c>
+      <c r="B751" s="3" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>30184</v>
+      </c>
+      <c r="B752" s="5" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>30185</v>
+      </c>
+      <c r="B753" s="3" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>30186</v>
+      </c>
+      <c r="B754" s="3" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>30187</v>
+      </c>
+      <c r="B755" s="4" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>30188</v>
+      </c>
+      <c r="B756" s="4" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>30189</v>
+      </c>
+      <c r="B757" s="2" t="n">
+        <v>11.19</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>30190</v>
+      </c>
+      <c r="B758" s="3" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>30191</v>
+      </c>
+      <c r="B759" s="3" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>30192</v>
+      </c>
+      <c r="B760" s="3" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>30193</v>
+      </c>
+      <c r="B761" s="3" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>30194</v>
+      </c>
+      <c r="B762" s="3" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>30195</v>
+      </c>
+      <c r="B763" s="3" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>30196</v>
+      </c>
+      <c r="B764" s="3" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>30197</v>
+      </c>
+      <c r="B765" s="2" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>30198</v>
+      </c>
+      <c r="B766" s="3" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>30199</v>
+      </c>
+      <c r="B767" s="4" t="n">
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>30200</v>
+      </c>
+      <c r="B768" s="3" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>30201</v>
+      </c>
+      <c r="B769" s="5" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>30202</v>
+      </c>
+      <c r="B770" s="3" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>30203</v>
+      </c>
+      <c r="B771" s="5" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>30204</v>
+      </c>
+      <c r="B772" s="4" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>30205</v>
+      </c>
+      <c r="B773" s="5" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>30206</v>
+      </c>
+      <c r="B774" s="3" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>30207</v>
+      </c>
+      <c r="B775" s="5" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>30208</v>
+      </c>
+      <c r="B776" s="5" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>30209</v>
+      </c>
+      <c r="B777" s="5" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>30210</v>
+      </c>
+      <c r="B778" s="5" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>30211</v>
+      </c>
+      <c r="B779" s="3" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>30212</v>
+      </c>
+      <c r="B780" s="5" t="n">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>30213</v>
+      </c>
+      <c r="B781" s="2" t="n">
+        <v>17.93</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>30214</v>
+      </c>
+      <c r="B782" s="4" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>30215</v>
+      </c>
+      <c r="B783" s="3" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>30216</v>
+      </c>
+      <c r="B784" s="3" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>30217</v>
+      </c>
+      <c r="B785" s="5" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>30218</v>
+      </c>
+      <c r="B786" s="3" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>30219</v>
+      </c>
+      <c r="B787" s="5" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>30220</v>
+      </c>
+      <c r="B788" s="3" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>30221</v>
+      </c>
+      <c r="B789" s="3" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>30222</v>
+      </c>
+      <c r="B790" s="3" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>30223</v>
+      </c>
+      <c r="B791" s="2" t="n">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>30224</v>
+      </c>
+      <c r="B792" s="3" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>30225</v>
+      </c>
+      <c r="B793" s="4" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>30226</v>
+      </c>
+      <c r="B794" s="2" t="n">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>30227</v>
+      </c>
+      <c r="B795" s="2" t="n">
+        <v>29.03</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>30228</v>
+      </c>
+      <c r="B796" s="5" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>30229</v>
+      </c>
+      <c r="B797" s="3" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>30230</v>
+      </c>
+      <c r="B798" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>30231</v>
+      </c>
+      <c r="B799" s="3" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>30232</v>
+      </c>
+      <c r="B800" s="4" t="n">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>30233</v>
+      </c>
+      <c r="B801" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>30234</v>
+      </c>
+      <c r="B802" s="3" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>30235</v>
+      </c>
+      <c r="B803" s="3" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>30236</v>
+      </c>
+      <c r="B804" s="3" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>30237</v>
+      </c>
+      <c r="B805" s="5" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>30238</v>
+      </c>
+      <c r="B806" s="3" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>30239</v>
+      </c>
+      <c r="B807" s="3" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>30240</v>
+      </c>
+      <c r="B808" s="3" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>30241</v>
+      </c>
+      <c r="B809" s="4" t="n">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>30242</v>
+      </c>
+      <c r="B810" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>30243</v>
+      </c>
+      <c r="B811" s="5" t="n">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>30244</v>
+      </c>
+      <c r="B812" s="2" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>30245</v>
+      </c>
+      <c r="B813" s="3" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>30246</v>
+      </c>
+      <c r="B814" s="3" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>30247</v>
+      </c>
+      <c r="B815" s="2" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>30248</v>
+      </c>
+      <c r="B816" s="3" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>30249</v>
+      </c>
+      <c r="B817" s="3" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>30250</v>
+      </c>
+      <c r="B818" s="4" t="n">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>30251</v>
+      </c>
+      <c r="B819" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>30252</v>
+      </c>
+      <c r="B820" s="3" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>30253</v>
+      </c>
+      <c r="B821" s="5" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>30254</v>
+      </c>
+      <c r="B822" s="5" t="n">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>30255</v>
+      </c>
+      <c r="B823" s="2" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>30256</v>
+      </c>
+      <c r="B824" s="5" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>30257</v>
+      </c>
+      <c r="B825" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>30258</v>
+      </c>
+      <c r="B826" s="3" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>30259</v>
+      </c>
+      <c r="B827" s="2" t="n">
+        <v>24.58</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>30260</v>
+      </c>
+      <c r="B828" s="2" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>30261</v>
+      </c>
+      <c r="B829" s="5" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>30262</v>
+      </c>
+      <c r="B830" s="5" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>30263</v>
+      </c>
+      <c r="B831" s="4" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>30264</v>
+      </c>
+      <c r="B832" s="2" t="n">
+        <v>11.46</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>30265</v>
+      </c>
+      <c r="B833" s="5" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>30266</v>
+      </c>
+      <c r="B834" s="2" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>30267</v>
+      </c>
+      <c r="B835" s="5" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>30268</v>
+      </c>
+      <c r="B836" s="2" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>30269</v>
+      </c>
+      <c r="B837" s="5" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>30270</v>
+      </c>
+      <c r="B838" s="5" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>30271</v>
+      </c>
+      <c r="B839" s="5" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>30272</v>
+      </c>
+      <c r="B840" s="3" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>30273</v>
+      </c>
+      <c r="B841" s="3" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>30274</v>
+      </c>
+      <c r="B842" s="5" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>30275</v>
+      </c>
+      <c r="B843" s="3" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>30276</v>
+      </c>
+      <c r="B844" s="5" t="n">
+        <v>4.44</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>30277</v>
+      </c>
+      <c r="B845" s="3" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>30278</v>
+      </c>
+      <c r="B846" s="3" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>30279</v>
+      </c>
+      <c r="B847" s="5" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>30280</v>
+      </c>
+      <c r="B848" s="5" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>30281</v>
+      </c>
+      <c r="B849" s="3" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>30282</v>
+      </c>
+      <c r="B850" s="5" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>30283</v>
+      </c>
+      <c r="B851" s="2" t="n">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>30284</v>
+      </c>
+      <c r="B852" s="2" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>30285</v>
+      </c>
+      <c r="B853" s="3" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>30286</v>
+      </c>
+      <c r="B854" s="4" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>30287</v>
+      </c>
+      <c r="B855" s="5" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>30288</v>
+      </c>
+      <c r="B856" s="3" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>30289</v>
+      </c>
+      <c r="B857" s="4" t="n">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>30290</v>
+      </c>
+      <c r="B858" s="4" t="n">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>30291</v>
+      </c>
+      <c r="B859" s="2" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>30292</v>
+      </c>
+      <c r="B860" s="2" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>30293</v>
+      </c>
+      <c r="B861" s="4" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>30294</v>
+      </c>
+      <c r="B862" s="5" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>30295</v>
+      </c>
+      <c r="B863" s="3" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>30296</v>
+      </c>
+      <c r="B864" s="3" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>30297</v>
+      </c>
+      <c r="B865" s="3" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>30298</v>
+      </c>
+      <c r="B866" s="3" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>30299</v>
+      </c>
+      <c r="B867" s="3" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>30300</v>
+      </c>
+      <c r="B868" s="2" t="n">
+        <v>12.81</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>30301</v>
+      </c>
+      <c r="B869" s="3" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>30302</v>
+      </c>
+      <c r="B870" s="4" t="n">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>30303</v>
+      </c>
+      <c r="B871" s="4" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B872" s="3" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B873" s="3" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>30306</v>
+      </c>
+      <c r="B874" s="4" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>30307</v>
+      </c>
+      <c r="B875" s="5" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>30308</v>
+      </c>
+      <c r="B876" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>30309</v>
+      </c>
+      <c r="B877" s="4" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>30310</v>
+      </c>
+      <c r="B878" s="3" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>30311</v>
+      </c>
+      <c r="B879" s="3" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>30312</v>
+      </c>
+      <c r="B880" s="3" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>30313</v>
+      </c>
+      <c r="B881" s="5" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>30314</v>
+      </c>
+      <c r="B882" s="5" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>30315</v>
+      </c>
+      <c r="B883" s="3" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>30316</v>
+      </c>
+      <c r="B884" s="3" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>30317</v>
+      </c>
+      <c r="B885" s="5" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>30318</v>
+      </c>
+      <c r="B886" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>30319</v>
+      </c>
+      <c r="B887" s="3" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>30320</v>
+      </c>
+      <c r="B888" s="3" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>30321</v>
+      </c>
+      <c r="B889" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>30322</v>
+      </c>
+      <c r="B890" s="3" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>30323</v>
+      </c>
+      <c r="B891" s="5" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>30324</v>
+      </c>
+      <c r="B892" s="5" t="n">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>30325</v>
+      </c>
+      <c r="B893" s="3" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>30326</v>
+      </c>
+      <c r="B894" s="5" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>30327</v>
+      </c>
+      <c r="B895" s="3" t="n">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>30328</v>
+      </c>
+      <c r="B896" s="3" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>30329</v>
+      </c>
+      <c r="B897" s="4" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>30330</v>
+      </c>
+      <c r="B898" s="3" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>30331</v>
+      </c>
+      <c r="B899" s="5" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>30332</v>
+      </c>
+      <c r="B900" s="2" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>30333</v>
+      </c>
+      <c r="B901" s="3" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>30334</v>
+      </c>
+      <c r="B902" s="2" t="n">
+        <v>101.59</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>30335</v>
+      </c>
+      <c r="B903" s="3" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>30336</v>
+      </c>
+      <c r="B904" s="3" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>30337</v>
+      </c>
+      <c r="B905" s="5" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>30338</v>
+      </c>
+      <c r="B906" s="3" t="n">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>30339</v>
+      </c>
+      <c r="B907" s="3" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>30340</v>
+      </c>
+      <c r="B908" s="5" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>30341</v>
+      </c>
+      <c r="B909" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>30342</v>
+      </c>
+      <c r="B910" s="3" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>30343</v>
+      </c>
+      <c r="B911" s="5" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>30344</v>
+      </c>
+      <c r="B912" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>30345</v>
+      </c>
+      <c r="B913" s="5" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>30346</v>
+      </c>
+      <c r="B914" s="4" t="n">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>30347</v>
+      </c>
+      <c r="B915" s="4" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>30348</v>
+      </c>
+      <c r="B916" s="5" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>30349</v>
+      </c>
+      <c r="B917" s="3" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>30350</v>
+      </c>
+      <c r="B918" s="3" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>30351</v>
+      </c>
+      <c r="B919" s="2" t="n">
+        <v>21.66</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>30352</v>
+      </c>
+      <c r="B920" s="3" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>30353</v>
+      </c>
+      <c r="B921" s="2" t="n">
+        <v>9.35</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>30354</v>
+      </c>
+      <c r="B922" s="5" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>30355</v>
+      </c>
+      <c r="B923" s="3" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>30356</v>
+      </c>
+      <c r="B924" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>30357</v>
+      </c>
+      <c r="B925" s="3" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>30358</v>
+      </c>
+      <c r="B926" s="3" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>30359</v>
+      </c>
+      <c r="B927" s="3" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>30360</v>
+      </c>
+      <c r="B928" s="5" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>30361</v>
+      </c>
+      <c r="B929" s="3" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>30362</v>
+      </c>
+      <c r="B930" s="3" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>30363</v>
+      </c>
+      <c r="B931" s="2" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>30364</v>
+      </c>
+      <c r="B932" s="5" t="n">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>30365</v>
+      </c>
+      <c r="B933" s="2" t="n">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>30366</v>
+      </c>
+      <c r="B934" s="2" t="n">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>30367</v>
+      </c>
+      <c r="B935" s="4" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>30368</v>
+      </c>
+      <c r="B936" s="5" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>30369</v>
+      </c>
+      <c r="B937" s="5" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>30370</v>
+      </c>
+      <c r="B938" s="2" t="n">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>30371</v>
+      </c>
+      <c r="B939" s="2" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>30372</v>
+      </c>
+      <c r="B940" s="5" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>30373</v>
+      </c>
+      <c r="B941" s="5" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>30374</v>
+      </c>
+      <c r="B942" s="2" t="n">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>30375</v>
+      </c>
+      <c r="B943" s="4" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>30376</v>
+      </c>
+      <c r="B944" s="3" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>30377</v>
+      </c>
+      <c r="B945" s="5" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>30378</v>
+      </c>
+      <c r="B946" s="5" t="n">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>30379</v>
+      </c>
+      <c r="B947" s="3" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>30380</v>
+      </c>
+      <c r="B948" s="2" t="n">
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>30381</v>
+      </c>
+      <c r="B949" s="2" t="n">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>30382</v>
+      </c>
+      <c r="B950" s="3" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>30383</v>
+      </c>
+      <c r="B951" s="3" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>30384</v>
+      </c>
+      <c r="B952" s="3" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>30385</v>
+      </c>
+      <c r="B953" s="3" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>30386</v>
+      </c>
+      <c r="B954" s="3" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>30387</v>
+      </c>
+      <c r="B955" s="3" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>30388</v>
+      </c>
+      <c r="B956" s="5" t="n">
+        <v>4.44</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>30389</v>
+      </c>
+      <c r="B957" s="4" t="n">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>30390</v>
+      </c>
+      <c r="B958" s="5" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>30391</v>
+      </c>
+      <c r="B959" s="2" t="n">
+        <v>7.11</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>30392</v>
+      </c>
+      <c r="B960" s="4" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>30393</v>
+      </c>
+      <c r="B961" s="5" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>30394</v>
+      </c>
+      <c r="B962" s="2" t="n">
+        <v>23.65</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>30395</v>
+      </c>
+      <c r="B963" s="5" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>30396</v>
+      </c>
+      <c r="B964" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>30397</v>
+      </c>
+      <c r="B965" s="5" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>30398</v>
+      </c>
+      <c r="B966" s="2" t="n">
+        <v>14.59</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>30399</v>
+      </c>
+      <c r="B967" s="3" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>30400</v>
+      </c>
+      <c r="B968" s="3" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>30401</v>
+      </c>
+      <c r="B969" s="3" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>30402</v>
+      </c>
+      <c r="B970" s="2" t="n">
+        <v>9.220000000000001</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>30403</v>
+      </c>
+      <c r="B971" s="5" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B972" s="3" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>30405</v>
+      </c>
+      <c r="B973" s="2" t="n">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>30406</v>
+      </c>
+      <c r="B974" s="2" t="n">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>30407</v>
+      </c>
+      <c r="B975" s="3" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>30408</v>
+      </c>
+      <c r="B976" s="4" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>30409</v>
+      </c>
+      <c r="B977" s="3" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>30410</v>
+      </c>
+      <c r="B978" s="3" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>30411</v>
+      </c>
+      <c r="B979" s="2" t="n">
+        <v>7.37</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>30412</v>
+      </c>
+      <c r="B980" s="3" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>30413</v>
+      </c>
+      <c r="B981" s="4" t="n">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>30414</v>
+      </c>
+      <c r="B982" s="5" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>30415</v>
+      </c>
+      <c r="B983" s="3" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>30416</v>
+      </c>
+      <c r="B984" s="2" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>30417</v>
+      </c>
+      <c r="B985" s="3" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>30418</v>
+      </c>
+      <c r="B986" s="5" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>30419</v>
+      </c>
+      <c r="B987" s="3" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>30420</v>
+      </c>
+      <c r="B988" s="3" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>30421</v>
+      </c>
+      <c r="B989" s="3" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>30422</v>
+      </c>
+      <c r="B990" s="5" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>30423</v>
+      </c>
+      <c r="B991" s="3" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>30424</v>
+      </c>
+      <c r="B992" s="4" t="n">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="n">
+        <v>30425</v>
+      </c>
+      <c r="B993" s="5" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="n">
+        <v>30426</v>
+      </c>
+      <c r="B994" s="3" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="n">
+        <v>30427</v>
+      </c>
+      <c r="B995" s="3" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="n">
+        <v>30428</v>
+      </c>
+      <c r="B996" s="4" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="n">
+        <v>30429</v>
+      </c>
+      <c r="B997" s="2" t="n">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="n">
+        <v>30430</v>
+      </c>
+      <c r="B998" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="n">
+        <v>30431</v>
+      </c>
+      <c r="B999" s="3" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="n">
+        <v>30432</v>
+      </c>
+      <c r="B1000" s="3" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>30433</v>
+      </c>
+      <c r="B1001" s="4" t="n">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="n">
+        <v>30434</v>
+      </c>
+      <c r="B1002" s="2" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="n">
+        <v>30435</v>
+      </c>
+      <c r="B1003" s="3" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="n">
+        <v>30436</v>
+      </c>
+      <c r="B1004" s="3" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="n">
+        <v>30437</v>
+      </c>
+      <c r="B1005" s="3" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="n">
+        <v>30438</v>
+      </c>
+      <c r="B1006" s="5" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="n">
+        <v>30439</v>
+      </c>
+      <c r="B1007" s="3" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="n">
+        <v>30440</v>
+      </c>
+      <c r="B1008" s="3" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="n">
+        <v>30441</v>
+      </c>
+      <c r="B1009" s="3" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n">
+        <v>30442</v>
+      </c>
+      <c r="B1010" s="3" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="n">
+        <v>30443</v>
+      </c>
+      <c r="B1011" s="5" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="n">
+        <v>30444</v>
+      </c>
+      <c r="B1012" s="2" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="n">
+        <v>30445</v>
+      </c>
+      <c r="B1013" s="3" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="n">
+        <v>30446</v>
+      </c>
+      <c r="B1014" s="3" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="n">
+        <v>30447</v>
+      </c>
+      <c r="B1015" s="5" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="n">
+        <v>30448</v>
+      </c>
+      <c r="B1016" s="5" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="n">
+        <v>30449</v>
+      </c>
+      <c r="B1017" s="3" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="n">
+        <v>30450</v>
+      </c>
+      <c r="B1018" s="3" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="n">
+        <v>30451</v>
+      </c>
+      <c r="B1019" s="5" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="n">
+        <v>30452</v>
+      </c>
+      <c r="B1020" s="3" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="n">
+        <v>30453</v>
+      </c>
+      <c r="B1021" s="3" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="n">
+        <v>30454</v>
+      </c>
+      <c r="B1022" s="3" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="n">
+        <v>30455</v>
+      </c>
+      <c r="B1023" s="3" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="n">
+        <v>30456</v>
+      </c>
+      <c r="B1024" s="3" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="n">
+        <v>30458</v>
+      </c>
+      <c r="B1025" s="2" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="n">
+        <v>30459</v>
+      </c>
+      <c r="B1026" s="4" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="n">
+        <v>30460</v>
+      </c>
+      <c r="B1027" s="5" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="n">
+        <v>30461</v>
+      </c>
+      <c r="B1028" s="3" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/1_apps/linux/sjudas/confinamento_batidas_trendline/dados_processados.xlsx
+++ b/1_apps/linux/sjudas/confinamento_batidas_trendline/dados_processados.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+        <bgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FF0000"/>
         <bgColor rgb="00FF0000"/>
       </patternFill>
@@ -53,12 +59,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-        <bgColor rgb="00FF9999"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -86,8 +86,8 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B465"/>
+  <dimension ref="A1:B964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,3714 +470,7706 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31529</v>
+        <v>31467</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.79</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>31530</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>6.11</v>
+        <v>31468</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31531</v>
+        <v>31469</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.81</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31532</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>31470</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>31533</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5.01</v>
+        <v>31471</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>31534</v>
+        <v>31472</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.77</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31535</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>5.2</v>
+        <v>31473</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>31536</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1.94</v>
+        <v>31474</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>12.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>31537</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>3.2</v>
+        <v>31475</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>31538</v>
+        <v>31476</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>8.44</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>31539</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>3.27</v>
+        <v>31477</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31540</v>
+        <v>31478</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3.16</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31541</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1.82</v>
+        <v>31479</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>31542</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>3.39</v>
+        <v>31480</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31543</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>1.5</v>
+        <v>31481</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31544</v>
+        <v>31482</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.9</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>31545</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>6.61</v>
+        <v>31483</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>7.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31546</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>2.51</v>
+        <v>31484</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>11.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31547</v>
+        <v>31485</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>3.33</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31548</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>4.07</v>
+        <v>31486</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>4.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>31549</v>
+        <v>31487</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.23</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>31550</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>5.91</v>
+        <v>31488</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>24.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>31551</v>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>3.55</v>
+        <v>31489</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31552</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>3.88</v>
+        <v>31490</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31553</v>
+        <v>31491</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>3.84</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>31554</v>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>4.35</v>
+        <v>31492</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>3.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31555</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>6.02</v>
+        <v>31493</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>7.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31556</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>31494</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31557</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>6.96</v>
+        <v>31495</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31558</v>
+        <v>31496</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>20.51</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31560</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>1.66</v>
+        <v>31497</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31561</v>
+        <v>31498</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2.63</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>31562</v>
+        <v>31499</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>4.96</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>31563</v>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>6.88</v>
+        <v>31500</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>31564</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>1.49</v>
+        <v>31501</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>3.63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>31565</v>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>4.69</v>
+        <v>31502</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>5.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31566</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>13.51</v>
+        <v>31503</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>12.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>31567</v>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>4.52</v>
+        <v>31504</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>31568</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>1.83</v>
+        <v>31505</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>26.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>31569</v>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>10.77</v>
+        <v>31506</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>6.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>31570</v>
+        <v>31507</v>
       </c>
       <c r="B42" s="4" t="n">
-        <v>26.39</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>31571</v>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>5.05</v>
+        <v>31508</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>7.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>31572</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>40.89</v>
+        <v>31509</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>16.18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>31573</v>
+        <v>31510</v>
       </c>
       <c r="B45" s="4" t="n">
-        <v>12.48</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>31574</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>4.35</v>
+        <v>31511</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>31575</v>
+        <v>31512</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>3.38</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>31576</v>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>5.96</v>
+        <v>31513</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>94.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>31577</v>
+        <v>31514</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>3.49</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>31578</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>29.49</v>
+        <v>31515</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>4.72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>31579</v>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>1.69</v>
+        <v>31516</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>18.21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>31580</v>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>1.13</v>
+        <v>31517</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>196.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>31581</v>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>11.68</v>
+        <v>31518</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>31582</v>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>17.9</v>
+        <v>31519</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>10.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>31583</v>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>2.03</v>
+        <v>31520</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>31584</v>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>1.42</v>
+        <v>31521</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>4.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31585</v>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>8.49</v>
+        <v>31522</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>3.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>31586</v>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>59.14</v>
+        <v>31523</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>17.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>31587</v>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>5.28</v>
+        <v>31524</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>6.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>31588</v>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>4.47</v>
+        <v>31525</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>5.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>31589</v>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>6.5</v>
+        <v>31526</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>14.31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>31590</v>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>3.09</v>
+        <v>31527</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>5.86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>31591</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>3.08</v>
+        <v>31528</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>4.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>31592</v>
+        <v>31529</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>1.08</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>31593</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>4.65</v>
+        <v>31530</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>6.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>31594</v>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>2.04</v>
+        <v>31531</v>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>31595</v>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>2.73</v>
+        <v>31532</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>31596</v>
-      </c>
-      <c r="B68" s="5" t="n">
-        <v>4.81</v>
+        <v>31533</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>5.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>31597</v>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>6.02</v>
+        <v>31534</v>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>31598</v>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>13.12</v>
+        <v>31535</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>5.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>31599</v>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>0.32</v>
+        <v>31536</v>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>31600</v>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>0.72</v>
+        <v>31537</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>31601</v>
-      </c>
-      <c r="B73" s="4" t="n">
-        <v>9.130000000000001</v>
+        <v>31538</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>8.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>31602</v>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>2.25</v>
+        <v>31539</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>31603</v>
-      </c>
-      <c r="B75" s="4" t="n">
-        <v>8.359999999999999</v>
+        <v>31540</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>3.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>31604</v>
+        <v>31541</v>
       </c>
       <c r="B76" s="4" t="n">
-        <v>18.42</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>31605</v>
-      </c>
-      <c r="B77" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>31542</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>3.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>31606</v>
+        <v>31543</v>
       </c>
       <c r="B78" s="4" t="n">
-        <v>7.74</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>31607</v>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>3.16</v>
+        <v>31544</v>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>31608</v>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>5.65</v>
+        <v>31545</v>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>6.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>31609</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>3.66</v>
+        <v>31546</v>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>2.51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>31610</v>
-      </c>
-      <c r="B82" s="5" t="n">
-        <v>3.5</v>
+        <v>31547</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>31611</v>
-      </c>
-      <c r="B83" s="4" t="n">
-        <v>14.85</v>
+        <v>31548</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>4.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>31612</v>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>2.02</v>
+        <v>31549</v>
+      </c>
+      <c r="B84" s="4" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>31613</v>
-      </c>
-      <c r="B85" s="5" t="n">
-        <v>4.83</v>
+        <v>31550</v>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>5.91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>31614</v>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>1.79</v>
+        <v>31551</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>31615</v>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>2.78</v>
+        <v>31552</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>3.88</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>31616</v>
+        <v>31553</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>5.89</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>31617</v>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>8.26</v>
+        <v>31554</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>4.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>31618</v>
+        <v>31555</v>
       </c>
       <c r="B90" s="3" t="n">
-        <v>2.61</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>31619</v>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>4.45</v>
+        <v>31556</v>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>31620</v>
-      </c>
-      <c r="B92" s="5" t="n">
-        <v>3.42</v>
+        <v>31557</v>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>6.96</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>31621</v>
-      </c>
-      <c r="B93" s="4" t="n">
-        <v>19.11</v>
+        <v>31558</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>20.51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>31622</v>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>1.74</v>
+        <v>31560</v>
+      </c>
+      <c r="B94" s="4" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>31623</v>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>2.62</v>
+        <v>31561</v>
+      </c>
+      <c r="B95" s="4" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>31624</v>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>2.85</v>
+        <v>31562</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>4.96</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>31625</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>3.33</v>
+        <v>31563</v>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>6.88</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>31626</v>
-      </c>
-      <c r="B98" s="5" t="n">
-        <v>3.53</v>
+        <v>31564</v>
+      </c>
+      <c r="B98" s="4" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>31627</v>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>2.43</v>
+        <v>31565</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>4.69</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>31628</v>
+        <v>31566</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>3.57</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>31629</v>
-      </c>
-      <c r="B101" s="5" t="n">
-        <v>3.35</v>
+        <v>31567</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>4.52</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>31630</v>
-      </c>
-      <c r="B102" s="5" t="n">
-        <v>3.52</v>
+        <v>31568</v>
+      </c>
+      <c r="B102" s="4" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>31631</v>
+        <v>31569</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>3.99</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>31632</v>
+        <v>31570</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>4.12</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>31633</v>
+        <v>31571</v>
       </c>
       <c r="B105" s="3" t="n">
-        <v>2.47</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>31634</v>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>2.16</v>
+        <v>31572</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>40.89</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>31635</v>
-      </c>
-      <c r="B107" s="4" t="n">
-        <v>7.43</v>
+        <v>31573</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>12.48</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>31636</v>
+        <v>31574</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6.52</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>31637</v>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>3.96</v>
+        <v>31575</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>3.38</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>31638</v>
+        <v>31576</v>
       </c>
       <c r="B110" s="3" t="n">
-        <v>2.03</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>31639</v>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>3.45</v>
+        <v>31577</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>3.49</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>31640</v>
-      </c>
-      <c r="B112" s="2" t="n">
-        <v>6.8</v>
+        <v>31578</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>29.49</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>31641</v>
-      </c>
-      <c r="B113" s="5" t="n">
-        <v>3.55</v>
+        <v>31579</v>
+      </c>
+      <c r="B113" s="4" t="n">
+        <v>1.69</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>31642</v>
-      </c>
-      <c r="B114" s="2" t="n">
-        <v>5.28</v>
+        <v>31580</v>
+      </c>
+      <c r="B114" s="4" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>31643</v>
+        <v>31581</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>4.38</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>31644</v>
-      </c>
-      <c r="B116" s="2" t="n">
-        <v>5.99</v>
+        <v>31582</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>17.9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>31645</v>
+        <v>31583</v>
       </c>
       <c r="B117" s="4" t="n">
-        <v>7.41</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>31646</v>
-      </c>
-      <c r="B118" s="2" t="n">
-        <v>5.57</v>
+        <v>31584</v>
+      </c>
+      <c r="B118" s="4" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>31647</v>
-      </c>
-      <c r="B119" s="2" t="n">
-        <v>5.45</v>
+        <v>31585</v>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>8.49</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>31648</v>
+        <v>31586</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>4.06</v>
+        <v>59.14</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>31649</v>
-      </c>
-      <c r="B121" s="4" t="n">
-        <v>22.8</v>
+        <v>31587</v>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>5.28</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>31650</v>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>2.07</v>
+        <v>31588</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>4.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>31651</v>
-      </c>
-      <c r="B123" s="5" t="n">
-        <v>4.34</v>
+        <v>31589</v>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>31652</v>
-      </c>
-      <c r="B124" s="5" t="n">
-        <v>4.72</v>
+        <v>31590</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>3.09</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>31653</v>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>3.2</v>
+        <v>31591</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>3.08</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>31654</v>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>1.77</v>
+        <v>31592</v>
+      </c>
+      <c r="B126" s="4" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>31655</v>
-      </c>
-      <c r="B127" s="5" t="n">
-        <v>4.15</v>
+        <v>31593</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>4.65</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>31656</v>
-      </c>
-      <c r="B128" s="5" t="n">
-        <v>3.58</v>
+        <v>31594</v>
+      </c>
+      <c r="B128" s="4" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>31657</v>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>0.18</v>
+        <v>31595</v>
+      </c>
+      <c r="B129" s="4" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>31658</v>
-      </c>
-      <c r="B130" s="5" t="n">
-        <v>4.01</v>
+        <v>31596</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>4.81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>31659</v>
+        <v>31597</v>
       </c>
       <c r="B131" s="3" t="n">
-        <v>1.78</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>31660</v>
+        <v>31598</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>4.89</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>31661</v>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>1.99</v>
+        <v>31599</v>
+      </c>
+      <c r="B133" s="4" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>31662</v>
-      </c>
-      <c r="B134" s="5" t="n">
-        <v>3.53</v>
+        <v>31600</v>
+      </c>
+      <c r="B134" s="4" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>31663</v>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>1.67</v>
+        <v>31601</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>31664</v>
-      </c>
-      <c r="B136" s="2" t="n">
-        <v>5.67</v>
+        <v>31602</v>
+      </c>
+      <c r="B136" s="4" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>31665</v>
-      </c>
-      <c r="B137" s="4" t="n">
-        <v>21.43</v>
+        <v>31603</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>31666</v>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>2.94</v>
+        <v>31604</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>18.42</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>31667</v>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>2.49</v>
+        <v>31605</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>31668</v>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>2.81</v>
+        <v>31606</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>7.74</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>31669</v>
-      </c>
-      <c r="B141" s="5" t="n">
-        <v>3.39</v>
+        <v>31607</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>3.16</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>31670</v>
+        <v>31608</v>
       </c>
       <c r="B142" s="3" t="n">
-        <v>1.13</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>31671</v>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>1.42</v>
+        <v>31609</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>3.66</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>31672</v>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>4.82</v>
+        <v>31610</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>31673</v>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>2.38</v>
+        <v>31611</v>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>14.85</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>31674</v>
-      </c>
-      <c r="B146" s="5" t="n">
-        <v>4.38</v>
+        <v>31612</v>
+      </c>
+      <c r="B146" s="4" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>31675</v>
-      </c>
-      <c r="B147" s="4" t="n">
-        <v>10.14</v>
+        <v>31613</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>4.83</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>31676</v>
-      </c>
-      <c r="B148" s="5" t="n">
-        <v>4.11</v>
+        <v>31614</v>
+      </c>
+      <c r="B148" s="4" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>31677</v>
-      </c>
-      <c r="B149" s="2" t="n">
-        <v>5.6</v>
+        <v>31615</v>
+      </c>
+      <c r="B149" s="4" t="n">
+        <v>2.78</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>31678</v>
+        <v>31616</v>
       </c>
       <c r="B150" s="3" t="n">
-        <v>2.09</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>31679</v>
-      </c>
-      <c r="B151" s="3" t="n">
-        <v>0.76</v>
+        <v>31617</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>8.26</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>31680</v>
-      </c>
-      <c r="B152" s="3" t="n">
-        <v>2.64</v>
+        <v>31618</v>
+      </c>
+      <c r="B152" s="4" t="n">
+        <v>2.61</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>31681</v>
-      </c>
-      <c r="B153" s="4" t="n">
-        <v>40.44</v>
+        <v>31619</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>4.45</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>31682</v>
-      </c>
-      <c r="B154" s="5" t="n">
-        <v>4.04</v>
+        <v>31620</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>31683</v>
-      </c>
-      <c r="B155" s="3" t="n">
-        <v>2.35</v>
+        <v>31621</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>19.11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>31684</v>
+        <v>31622</v>
       </c>
       <c r="B156" s="4" t="n">
-        <v>8.390000000000001</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>31685</v>
-      </c>
-      <c r="B157" s="3" t="n">
-        <v>2.95</v>
+        <v>31623</v>
+      </c>
+      <c r="B157" s="4" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>31686</v>
-      </c>
-      <c r="B158" s="3" t="n">
-        <v>2.52</v>
+        <v>31624</v>
+      </c>
+      <c r="B158" s="4" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>31687</v>
+        <v>31625</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>5.97</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>31688</v>
-      </c>
-      <c r="B160" s="4" t="n">
-        <v>14.79</v>
+        <v>31626</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>3.53</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>31689</v>
-      </c>
-      <c r="B161" s="3" t="n">
-        <v>1.42</v>
+        <v>31627</v>
+      </c>
+      <c r="B161" s="4" t="n">
+        <v>2.43</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>31690</v>
-      </c>
-      <c r="B162" s="5" t="n">
-        <v>3.11</v>
+        <v>31628</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>3.57</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>31691</v>
-      </c>
-      <c r="B163" s="4" t="n">
-        <v>9.02</v>
+        <v>31629</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>31692</v>
-      </c>
-      <c r="B164" s="5" t="n">
-        <v>4.32</v>
+        <v>31630</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>3.52</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>31693</v>
-      </c>
-      <c r="B165" s="5" t="n">
-        <v>4.82</v>
+        <v>31631</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>31694</v>
-      </c>
-      <c r="B166" s="4" t="n">
-        <v>14.33</v>
+        <v>31632</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>4.12</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>31695</v>
+        <v>31633</v>
       </c>
       <c r="B167" s="4" t="n">
-        <v>20.12</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>31696</v>
+        <v>31634</v>
       </c>
       <c r="B168" s="4" t="n">
-        <v>7.69</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>31697</v>
-      </c>
-      <c r="B169" s="2" t="n">
-        <v>6.75</v>
+        <v>31635</v>
+      </c>
+      <c r="B169" s="5" t="n">
+        <v>7.43</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>31698</v>
-      </c>
-      <c r="B170" s="2" t="n">
-        <v>5.5</v>
+        <v>31636</v>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>6.52</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>31699</v>
-      </c>
-      <c r="B171" s="5" t="n">
-        <v>4.85</v>
+        <v>31637</v>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>3.96</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>31700</v>
+        <v>31638</v>
       </c>
       <c r="B172" s="4" t="n">
-        <v>8.07</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>31701</v>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>2.43</v>
+        <v>31639</v>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>3.45</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>31702</v>
+        <v>31640</v>
       </c>
       <c r="B174" s="3" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>31703</v>
-      </c>
-      <c r="B175" s="4" t="n">
-        <v>9.65</v>
+        <v>31641</v>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>31704</v>
+        <v>31642</v>
       </c>
       <c r="B176" s="3" t="n">
-        <v>2.61</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>31705</v>
-      </c>
-      <c r="B177" s="3" t="n">
-        <v>2.76</v>
+        <v>31643</v>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>4.38</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>31706</v>
-      </c>
-      <c r="B178" s="4" t="n">
-        <v>7.32</v>
+        <v>31644</v>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>5.99</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>31707</v>
+        <v>31645</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>4.27</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>31708</v>
-      </c>
-      <c r="B180" s="2" t="n">
-        <v>5.44</v>
+        <v>31646</v>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>5.57</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>31709</v>
-      </c>
-      <c r="B181" s="4" t="n">
-        <v>17.98</v>
+        <v>31647</v>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>5.45</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>31710</v>
-      </c>
-      <c r="B182" s="5" t="n">
-        <v>4.39</v>
+        <v>31648</v>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>4.06</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>31711</v>
-      </c>
-      <c r="B183" s="4" t="n">
-        <v>9.5</v>
+        <v>31649</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>22.8</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>31712</v>
-      </c>
-      <c r="B184" s="5" t="n">
-        <v>3.24</v>
+        <v>31650</v>
+      </c>
+      <c r="B184" s="4" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>31713</v>
-      </c>
-      <c r="B185" s="5" t="n">
-        <v>4.91</v>
+        <v>31651</v>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>4.34</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>31714</v>
-      </c>
-      <c r="B186" s="4" t="n">
-        <v>13.21</v>
+        <v>31652</v>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>4.72</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>31715</v>
-      </c>
-      <c r="B187" s="3" t="n">
-        <v>1.69</v>
+        <v>31653</v>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>31716</v>
-      </c>
-      <c r="B188" s="3" t="n">
-        <v>2.59</v>
+        <v>31654</v>
+      </c>
+      <c r="B188" s="4" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>31717</v>
-      </c>
-      <c r="B189" s="5" t="n">
-        <v>4.59</v>
+        <v>31655</v>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>4.15</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>31718</v>
-      </c>
-      <c r="B190" s="3" t="n">
-        <v>1.66</v>
+        <v>31656</v>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>3.58</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>31719</v>
-      </c>
-      <c r="B191" s="3" t="n">
-        <v>1.88</v>
+        <v>31657</v>
+      </c>
+      <c r="B191" s="4" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>31720</v>
-      </c>
-      <c r="B192" s="3" t="n">
-        <v>1.67</v>
+        <v>31658</v>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>4.01</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>31721</v>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>2.95</v>
+        <v>31659</v>
+      </c>
+      <c r="B193" s="4" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>31722</v>
-      </c>
-      <c r="B194" s="3" t="n">
-        <v>1.27</v>
+        <v>31660</v>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>4.89</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>31723</v>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>1.58</v>
+        <v>31661</v>
+      </c>
+      <c r="B195" s="4" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>31724</v>
-      </c>
-      <c r="B196" s="3" t="n">
-        <v>1.94</v>
+        <v>31662</v>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>3.53</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>31725</v>
-      </c>
-      <c r="B197" s="3" t="n">
-        <v>2.56</v>
+        <v>31663</v>
+      </c>
+      <c r="B197" s="4" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>31726</v>
+        <v>31664</v>
       </c>
       <c r="B198" s="3" t="n">
-        <v>0.91</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>31727</v>
-      </c>
-      <c r="B199" s="3" t="n">
-        <v>1.21</v>
+        <v>31665</v>
+      </c>
+      <c r="B199" s="5" t="n">
+        <v>21.43</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>31728</v>
-      </c>
-      <c r="B200" s="3" t="n">
-        <v>2.68</v>
+        <v>31666</v>
+      </c>
+      <c r="B200" s="4" t="n">
+        <v>2.94</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>31729</v>
-      </c>
-      <c r="B201" s="5" t="n">
-        <v>3.47</v>
+        <v>31667</v>
+      </c>
+      <c r="B201" s="4" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>31730</v>
-      </c>
-      <c r="B202" s="3" t="n">
-        <v>1.87</v>
+        <v>31668</v>
+      </c>
+      <c r="B202" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>31731</v>
-      </c>
-      <c r="B203" s="3" t="n">
-        <v>1.28</v>
+        <v>31669</v>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>3.39</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>31732</v>
-      </c>
-      <c r="B204" s="2" t="n">
-        <v>5.24</v>
+        <v>31670</v>
+      </c>
+      <c r="B204" s="4" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>31733</v>
-      </c>
-      <c r="B205" s="5" t="n">
-        <v>4.03</v>
+        <v>31671</v>
+      </c>
+      <c r="B205" s="4" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>31734</v>
-      </c>
-      <c r="B206" s="3" t="n">
-        <v>1.86</v>
+        <v>31672</v>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>4.82</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>31735</v>
-      </c>
-      <c r="B207" s="3" t="n">
-        <v>1.57</v>
+        <v>31673</v>
+      </c>
+      <c r="B207" s="4" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>31736</v>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>2.33</v>
+        <v>31674</v>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>4.38</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>31737</v>
-      </c>
-      <c r="B209" s="3" t="n">
-        <v>2.13</v>
+        <v>31675</v>
+      </c>
+      <c r="B209" s="5" t="n">
+        <v>10.14</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>31738</v>
-      </c>
-      <c r="B210" s="3" t="n">
-        <v>1.69</v>
+        <v>31676</v>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>4.11</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>31739</v>
+        <v>31677</v>
       </c>
       <c r="B211" s="3" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>31740</v>
-      </c>
-      <c r="B212" s="3" t="n">
-        <v>0.77</v>
+        <v>31678</v>
+      </c>
+      <c r="B212" s="4" t="n">
+        <v>2.09</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>31741</v>
-      </c>
-      <c r="B213" s="5" t="n">
-        <v>3.3</v>
+        <v>31679</v>
+      </c>
+      <c r="B213" s="4" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>31742</v>
-      </c>
-      <c r="B214" s="3" t="n">
-        <v>1.51</v>
+        <v>31680</v>
+      </c>
+      <c r="B214" s="4" t="n">
+        <v>2.64</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>31743</v>
-      </c>
-      <c r="B215" s="3" t="n">
-        <v>1.34</v>
+        <v>31681</v>
+      </c>
+      <c r="B215" s="5" t="n">
+        <v>40.44</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>31744</v>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>2.31</v>
+        <v>31682</v>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>4.04</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>31745</v>
-      </c>
-      <c r="B217" s="5" t="n">
-        <v>3.39</v>
+        <v>31683</v>
+      </c>
+      <c r="B217" s="4" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>31746</v>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>2.07</v>
+        <v>31684</v>
+      </c>
+      <c r="B218" s="5" t="n">
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>31747</v>
-      </c>
-      <c r="B219" s="5" t="n">
-        <v>4.98</v>
+        <v>31685</v>
+      </c>
+      <c r="B219" s="4" t="n">
+        <v>2.95</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>31748</v>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>2.9</v>
+        <v>31686</v>
+      </c>
+      <c r="B220" s="4" t="n">
+        <v>2.52</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>31749</v>
-      </c>
-      <c r="B221" s="5" t="n">
-        <v>3.85</v>
+        <v>31687</v>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>5.97</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>31750</v>
+        <v>31688</v>
       </c>
       <c r="B222" s="5" t="n">
-        <v>4.39</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>31751</v>
-      </c>
-      <c r="B223" s="5" t="n">
-        <v>3.08</v>
+        <v>31689</v>
+      </c>
+      <c r="B223" s="4" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>31752</v>
-      </c>
-      <c r="B224" s="5" t="n">
-        <v>4.2</v>
+        <v>31690</v>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>3.11</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>31753</v>
-      </c>
-      <c r="B225" s="3" t="n">
-        <v>1.44</v>
+        <v>31691</v>
+      </c>
+      <c r="B225" s="5" t="n">
+        <v>9.02</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>31754</v>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>2.62</v>
+        <v>31692</v>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>4.32</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>31755</v>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>2.15</v>
+        <v>31693</v>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>4.82</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>31756</v>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>1.2</v>
+        <v>31694</v>
+      </c>
+      <c r="B228" s="5" t="n">
+        <v>14.33</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>31757</v>
-      </c>
-      <c r="B229" s="2" t="n">
-        <v>6.12</v>
+        <v>31695</v>
+      </c>
+      <c r="B229" s="5" t="n">
+        <v>20.12</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>31758</v>
-      </c>
-      <c r="B230" s="3" t="n">
-        <v>2.47</v>
+        <v>31696</v>
+      </c>
+      <c r="B230" s="5" t="n">
+        <v>7.69</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>31759</v>
+        <v>31697</v>
       </c>
       <c r="B231" s="3" t="n">
-        <v>2.58</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>31760</v>
+        <v>31698</v>
       </c>
       <c r="B232" s="3" t="n">
-        <v>0.61</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>31761</v>
-      </c>
-      <c r="B233" s="5" t="n">
-        <v>4.8</v>
+        <v>31699</v>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>4.85</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>31762</v>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>1.65</v>
+        <v>31700</v>
+      </c>
+      <c r="B234" s="5" t="n">
+        <v>8.07</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>31763</v>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>2.14</v>
+        <v>31701</v>
+      </c>
+      <c r="B235" s="4" t="n">
+        <v>2.43</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>31764</v>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>1.86</v>
+        <v>31702</v>
+      </c>
+      <c r="B236" s="4" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>31765</v>
+        <v>31703</v>
       </c>
       <c r="B237" s="5" t="n">
-        <v>4.33</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>31766</v>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>2.59</v>
+        <v>31704</v>
+      </c>
+      <c r="B238" s="4" t="n">
+        <v>2.61</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>31767</v>
-      </c>
-      <c r="B239" s="3" t="n">
-        <v>2.5</v>
+        <v>31705</v>
+      </c>
+      <c r="B239" s="4" t="n">
+        <v>2.76</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>31768</v>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>2.19</v>
+        <v>31706</v>
+      </c>
+      <c r="B240" s="5" t="n">
+        <v>7.32</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>31769</v>
+        <v>31707</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>6.52</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>31770</v>
-      </c>
-      <c r="B242" s="2" t="n">
-        <v>5.78</v>
+        <v>31708</v>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>5.44</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>31771</v>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>1.92</v>
+        <v>31709</v>
+      </c>
+      <c r="B243" s="5" t="n">
+        <v>17.98</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>31772</v>
+        <v>31710</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>5.79</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>31773</v>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>1.97</v>
+        <v>31711</v>
+      </c>
+      <c r="B245" s="5" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>31774</v>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>1.37</v>
+        <v>31712</v>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>31775</v>
-      </c>
-      <c r="B247" s="3" t="n">
-        <v>2.53</v>
+        <v>31713</v>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>4.91</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>31776</v>
-      </c>
-      <c r="B248" s="3" t="n">
-        <v>2.53</v>
+        <v>31714</v>
+      </c>
+      <c r="B248" s="5" t="n">
+        <v>13.21</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>31777</v>
-      </c>
-      <c r="B249" s="5" t="n">
-        <v>4.9</v>
+        <v>31715</v>
+      </c>
+      <c r="B249" s="4" t="n">
+        <v>1.69</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>31778</v>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>2.05</v>
+        <v>31716</v>
+      </c>
+      <c r="B250" s="4" t="n">
+        <v>2.59</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>31779</v>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>2.93</v>
+        <v>31717</v>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>4.59</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>31780</v>
-      </c>
-      <c r="B252" s="5" t="n">
-        <v>3.52</v>
+        <v>31718</v>
+      </c>
+      <c r="B252" s="4" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>31781</v>
-      </c>
-      <c r="B253" s="3" t="n">
-        <v>2.15</v>
+        <v>31719</v>
+      </c>
+      <c r="B253" s="4" t="n">
+        <v>1.88</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>31782</v>
+        <v>31720</v>
       </c>
       <c r="B254" s="4" t="n">
-        <v>10.97</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>31783</v>
+        <v>31721</v>
       </c>
       <c r="B255" s="4" t="n">
-        <v>37.03</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>31784</v>
-      </c>
-      <c r="B256" s="5" t="n">
-        <v>4.02</v>
+        <v>31722</v>
+      </c>
+      <c r="B256" s="4" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>31785</v>
-      </c>
-      <c r="B257" s="3" t="n">
-        <v>1.1</v>
+        <v>31723</v>
+      </c>
+      <c r="B257" s="4" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>31786</v>
-      </c>
-      <c r="B258" s="5" t="n">
-        <v>4.1</v>
+        <v>31724</v>
+      </c>
+      <c r="B258" s="4" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>31787</v>
-      </c>
-      <c r="B259" s="3" t="n">
-        <v>2.37</v>
+        <v>31725</v>
+      </c>
+      <c r="B259" s="4" t="n">
+        <v>2.56</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>31788</v>
-      </c>
-      <c r="B260" s="5" t="n">
-        <v>3.92</v>
+        <v>31726</v>
+      </c>
+      <c r="B260" s="4" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>31789</v>
-      </c>
-      <c r="B261" s="3" t="n">
-        <v>0.77</v>
+        <v>31727</v>
+      </c>
+      <c r="B261" s="4" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>31790</v>
-      </c>
-      <c r="B262" s="3" t="n">
-        <v>1.4</v>
+        <v>31728</v>
+      </c>
+      <c r="B262" s="4" t="n">
+        <v>2.68</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>31791</v>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>1.3</v>
+        <v>31729</v>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>3.47</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>31792</v>
-      </c>
-      <c r="B264" s="3" t="n">
-        <v>1.09</v>
+        <v>31730</v>
+      </c>
+      <c r="B264" s="4" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>31793</v>
-      </c>
-      <c r="B265" s="3" t="n">
-        <v>2.25</v>
+        <v>31731</v>
+      </c>
+      <c r="B265" s="4" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>31794</v>
-      </c>
-      <c r="B266" s="5" t="n">
-        <v>4.51</v>
+        <v>31732</v>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>5.24</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>31795</v>
-      </c>
-      <c r="B267" s="3" t="n">
-        <v>2.02</v>
+        <v>31733</v>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>4.03</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>31796</v>
-      </c>
-      <c r="B268" s="3" t="n">
-        <v>1.95</v>
+        <v>31734</v>
+      </c>
+      <c r="B268" s="4" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>31797</v>
-      </c>
-      <c r="B269" s="3" t="n">
-        <v>2.35</v>
+        <v>31735</v>
+      </c>
+      <c r="B269" s="4" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>31798</v>
-      </c>
-      <c r="B270" s="3" t="n">
-        <v>2.84</v>
+        <v>31736</v>
+      </c>
+      <c r="B270" s="4" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>31799</v>
-      </c>
-      <c r="B271" s="3" t="n">
-        <v>2.94</v>
+        <v>31737</v>
+      </c>
+      <c r="B271" s="4" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>31800</v>
-      </c>
-      <c r="B272" s="3" t="n">
-        <v>2.42</v>
+        <v>31738</v>
+      </c>
+      <c r="B272" s="4" t="n">
+        <v>1.69</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>31801</v>
-      </c>
-      <c r="B273" s="3" t="n">
-        <v>1.33</v>
+        <v>31739</v>
+      </c>
+      <c r="B273" s="4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>31802</v>
-      </c>
-      <c r="B274" s="3" t="n">
-        <v>1.74</v>
+        <v>31740</v>
+      </c>
+      <c r="B274" s="4" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>31803</v>
-      </c>
-      <c r="B275" s="3" t="n">
-        <v>1.55</v>
+        <v>31741</v>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>31804</v>
-      </c>
-      <c r="B276" s="3" t="n">
-        <v>1.01</v>
+        <v>31742</v>
+      </c>
+      <c r="B276" s="4" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>31805</v>
-      </c>
-      <c r="B277" s="5" t="n">
-        <v>4</v>
+        <v>31743</v>
+      </c>
+      <c r="B277" s="4" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>31806</v>
-      </c>
-      <c r="B278" s="3" t="n">
-        <v>1.33</v>
+        <v>31744</v>
+      </c>
+      <c r="B278" s="4" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>31807</v>
-      </c>
-      <c r="B279" s="3" t="n">
-        <v>0.8</v>
+        <v>31745</v>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>3.39</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>31808</v>
-      </c>
-      <c r="B280" s="5" t="n">
-        <v>3.65</v>
+        <v>31746</v>
+      </c>
+      <c r="B280" s="4" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>31809</v>
-      </c>
-      <c r="B281" s="3" t="n">
-        <v>1.64</v>
+        <v>31747</v>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>4.98</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>31810</v>
-      </c>
-      <c r="B282" s="3" t="n">
-        <v>2.22</v>
+        <v>31748</v>
+      </c>
+      <c r="B282" s="4" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>31811</v>
-      </c>
-      <c r="B283" s="5" t="n">
-        <v>3.08</v>
+        <v>31749</v>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>3.85</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>31812</v>
-      </c>
-      <c r="B284" s="3" t="n">
-        <v>2.13</v>
+        <v>31750</v>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>4.39</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>31813</v>
-      </c>
-      <c r="B285" s="5" t="n">
-        <v>3.57</v>
+        <v>31751</v>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>3.08</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>31814</v>
-      </c>
-      <c r="B286" s="5" t="n">
-        <v>3.57</v>
+        <v>31752</v>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>31815</v>
-      </c>
-      <c r="B287" s="2" t="n">
-        <v>6.62</v>
+        <v>31753</v>
+      </c>
+      <c r="B287" s="4" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>31816</v>
-      </c>
-      <c r="B288" s="5" t="n">
-        <v>4</v>
+        <v>31754</v>
+      </c>
+      <c r="B288" s="4" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>31817</v>
-      </c>
-      <c r="B289" s="3" t="n">
-        <v>2.35</v>
+        <v>31755</v>
+      </c>
+      <c r="B289" s="4" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>31818</v>
-      </c>
-      <c r="B290" s="3" t="n">
-        <v>2.62</v>
+        <v>31756</v>
+      </c>
+      <c r="B290" s="4" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>31819</v>
+        <v>31757</v>
       </c>
       <c r="B291" s="3" t="n">
-        <v>1.06</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>31820</v>
-      </c>
-      <c r="B292" s="3" t="n">
-        <v>1.27</v>
+        <v>31758</v>
+      </c>
+      <c r="B292" s="4" t="n">
+        <v>2.47</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>31821</v>
-      </c>
-      <c r="B293" s="3" t="n">
-        <v>1.92</v>
+        <v>31759</v>
+      </c>
+      <c r="B293" s="4" t="n">
+        <v>2.58</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>31822</v>
-      </c>
-      <c r="B294" s="5" t="n">
-        <v>3.24</v>
+        <v>31760</v>
+      </c>
+      <c r="B294" s="4" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>31823</v>
-      </c>
-      <c r="B295" s="3" t="n">
-        <v>2.27</v>
+        <v>31761</v>
+      </c>
+      <c r="B295" s="2" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>31824</v>
+        <v>31762</v>
       </c>
       <c r="B296" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>31825</v>
-      </c>
-      <c r="B297" s="3" t="n">
-        <v>2.01</v>
+        <v>31763</v>
+      </c>
+      <c r="B297" s="4" t="n">
+        <v>2.14</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>31826</v>
-      </c>
-      <c r="B298" s="3" t="n">
-        <v>1.94</v>
+        <v>31764</v>
+      </c>
+      <c r="B298" s="4" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>31827</v>
-      </c>
-      <c r="B299" s="3" t="n">
-        <v>2.11</v>
+        <v>31765</v>
+      </c>
+      <c r="B299" s="2" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>31828</v>
-      </c>
-      <c r="B300" s="3" t="n">
-        <v>2.71</v>
+        <v>31766</v>
+      </c>
+      <c r="B300" s="4" t="n">
+        <v>2.59</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>31829</v>
-      </c>
-      <c r="B301" s="3" t="n">
-        <v>2.92</v>
+        <v>31767</v>
+      </c>
+      <c r="B301" s="4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>31830</v>
+        <v>31768</v>
       </c>
       <c r="B302" s="4" t="n">
-        <v>13.5</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>31831</v>
+        <v>31769</v>
       </c>
       <c r="B303" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>31832</v>
+        <v>31770</v>
       </c>
       <c r="B304" s="3" t="n">
-        <v>1.21</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>31833</v>
+        <v>31771</v>
       </c>
       <c r="B305" s="4" t="n">
-        <v>12.76</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>31834</v>
-      </c>
-      <c r="B306" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>31772</v>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>5.79</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>31835</v>
-      </c>
-      <c r="B307" s="3" t="n">
-        <v>1.55</v>
+        <v>31773</v>
+      </c>
+      <c r="B307" s="4" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>31836</v>
-      </c>
-      <c r="B308" s="3" t="n">
-        <v>2.99</v>
+        <v>31774</v>
+      </c>
+      <c r="B308" s="4" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>31837</v>
+        <v>31775</v>
       </c>
       <c r="B309" s="4" t="n">
-        <v>10.79</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>31838</v>
-      </c>
-      <c r="B310" s="5" t="n">
-        <v>3.19</v>
+        <v>31776</v>
+      </c>
+      <c r="B310" s="4" t="n">
+        <v>2.53</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>31839</v>
-      </c>
-      <c r="B311" s="3" t="n">
-        <v>2.72</v>
+        <v>31777</v>
+      </c>
+      <c r="B311" s="2" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>31840</v>
-      </c>
-      <c r="B312" s="3" t="n">
-        <v>1.43</v>
+        <v>31778</v>
+      </c>
+      <c r="B312" s="4" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>31841</v>
-      </c>
-      <c r="B313" s="3" t="n">
-        <v>2.77</v>
+        <v>31779</v>
+      </c>
+      <c r="B313" s="4" t="n">
+        <v>2.93</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>31842</v>
-      </c>
-      <c r="B314" s="3" t="n">
-        <v>2.08</v>
+        <v>31780</v>
+      </c>
+      <c r="B314" s="2" t="n">
+        <v>3.52</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>31843</v>
-      </c>
-      <c r="B315" s="3" t="n">
-        <v>1.42</v>
+        <v>31781</v>
+      </c>
+      <c r="B315" s="4" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>31844</v>
-      </c>
-      <c r="B316" s="3" t="n">
-        <v>1.46</v>
+        <v>31782</v>
+      </c>
+      <c r="B316" s="5" t="n">
+        <v>10.97</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>31845</v>
-      </c>
-      <c r="B317" s="3" t="n">
-        <v>2.68</v>
+        <v>31783</v>
+      </c>
+      <c r="B317" s="5" t="n">
+        <v>37.03</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>31846</v>
-      </c>
-      <c r="B318" s="3" t="n">
-        <v>1.65</v>
+        <v>31784</v>
+      </c>
+      <c r="B318" s="2" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>31847</v>
+        <v>31785</v>
       </c>
       <c r="B319" s="4" t="n">
-        <v>11.32</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>31848</v>
-      </c>
-      <c r="B320" s="5" t="n">
-        <v>4.3</v>
+        <v>31786</v>
+      </c>
+      <c r="B320" s="2" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>31849</v>
-      </c>
-      <c r="B321" s="3" t="n">
-        <v>1.85</v>
+        <v>31787</v>
+      </c>
+      <c r="B321" s="4" t="n">
+        <v>2.37</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>31850</v>
-      </c>
-      <c r="B322" s="3" t="n">
-        <v>2.52</v>
+        <v>31788</v>
+      </c>
+      <c r="B322" s="2" t="n">
+        <v>3.92</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>31851</v>
-      </c>
-      <c r="B323" s="3" t="n">
-        <v>1.5</v>
+        <v>31789</v>
+      </c>
+      <c r="B323" s="4" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>31852</v>
-      </c>
-      <c r="B324" s="5" t="n">
-        <v>3.64</v>
+        <v>31790</v>
+      </c>
+      <c r="B324" s="4" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>31853</v>
-      </c>
-      <c r="B325" s="3" t="n">
-        <v>1.34</v>
+        <v>31791</v>
+      </c>
+      <c r="B325" s="4" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>31854</v>
+        <v>31792</v>
       </c>
       <c r="B326" s="4" t="n">
-        <v>11.32</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>31855</v>
-      </c>
-      <c r="B327" s="3" t="n">
-        <v>2.92</v>
+        <v>31793</v>
+      </c>
+      <c r="B327" s="4" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>31856</v>
-      </c>
-      <c r="B328" s="3" t="n">
-        <v>1.26</v>
+        <v>31794</v>
+      </c>
+      <c r="B328" s="2" t="n">
+        <v>4.51</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>31857</v>
-      </c>
-      <c r="B329" s="3" t="n">
-        <v>1.24</v>
+        <v>31795</v>
+      </c>
+      <c r="B329" s="4" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>31858</v>
-      </c>
-      <c r="B330" s="3" t="n">
-        <v>1.49</v>
+        <v>31796</v>
+      </c>
+      <c r="B330" s="4" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>31859</v>
-      </c>
-      <c r="B331" s="2" t="n">
-        <v>5.06</v>
+        <v>31797</v>
+      </c>
+      <c r="B331" s="4" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>31860</v>
-      </c>
-      <c r="B332" s="3" t="n">
-        <v>1.46</v>
+        <v>31798</v>
+      </c>
+      <c r="B332" s="4" t="n">
+        <v>2.84</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>31861</v>
-      </c>
-      <c r="B333" s="3" t="n">
-        <v>1.46</v>
+        <v>31799</v>
+      </c>
+      <c r="B333" s="4" t="n">
+        <v>2.94</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>31862</v>
-      </c>
-      <c r="B334" s="3" t="n">
-        <v>1.75</v>
+        <v>31800</v>
+      </c>
+      <c r="B334" s="4" t="n">
+        <v>2.42</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>31863</v>
-      </c>
-      <c r="B335" s="3" t="n">
-        <v>1.47</v>
+        <v>31801</v>
+      </c>
+      <c r="B335" s="4" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>31864</v>
-      </c>
-      <c r="B336" s="3" t="n">
-        <v>1.28</v>
+        <v>31802</v>
+      </c>
+      <c r="B336" s="4" t="n">
+        <v>1.74</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>31865</v>
-      </c>
-      <c r="B337" s="3" t="n">
-        <v>1.29</v>
+        <v>31803</v>
+      </c>
+      <c r="B337" s="4" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>31866</v>
-      </c>
-      <c r="B338" s="3" t="n">
-        <v>2.71</v>
+        <v>31804</v>
+      </c>
+      <c r="B338" s="4" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>31867</v>
-      </c>
-      <c r="B339" s="3" t="n">
-        <v>1.98</v>
+        <v>31805</v>
+      </c>
+      <c r="B339" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>31868</v>
-      </c>
-      <c r="B340" s="3" t="n">
-        <v>0.99</v>
+        <v>31806</v>
+      </c>
+      <c r="B340" s="4" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>31869</v>
-      </c>
-      <c r="B341" s="3" t="n">
-        <v>2.25</v>
+        <v>31807</v>
+      </c>
+      <c r="B341" s="4" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>31870</v>
-      </c>
-      <c r="B342" s="3" t="n">
-        <v>2.83</v>
+        <v>31808</v>
+      </c>
+      <c r="B342" s="2" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>31871</v>
-      </c>
-      <c r="B343" s="3" t="n">
-        <v>1.57</v>
+        <v>31809</v>
+      </c>
+      <c r="B343" s="4" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>31872</v>
-      </c>
-      <c r="B344" s="3" t="n">
-        <v>0.98</v>
+        <v>31810</v>
+      </c>
+      <c r="B344" s="4" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>31873</v>
-      </c>
-      <c r="B345" s="3" t="n">
-        <v>0.82</v>
+        <v>31811</v>
+      </c>
+      <c r="B345" s="2" t="n">
+        <v>3.08</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>31874</v>
-      </c>
-      <c r="B346" s="5" t="n">
-        <v>3.32</v>
+        <v>31812</v>
+      </c>
+      <c r="B346" s="4" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>31875</v>
-      </c>
-      <c r="B347" s="3" t="n">
-        <v>2.81</v>
+        <v>31813</v>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>3.57</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>31876</v>
-      </c>
-      <c r="B348" s="3" t="n">
-        <v>1.56</v>
+        <v>31814</v>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>3.57</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>31877</v>
-      </c>
-      <c r="B349" s="5" t="n">
-        <v>3.17</v>
+        <v>31815</v>
+      </c>
+      <c r="B349" s="3" t="n">
+        <v>6.62</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>31878</v>
-      </c>
-      <c r="B350" s="3" t="n">
-        <v>1.51</v>
+        <v>31816</v>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>31879</v>
-      </c>
-      <c r="B351" s="3" t="n">
-        <v>1.68</v>
+        <v>31817</v>
+      </c>
+      <c r="B351" s="4" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>31880</v>
-      </c>
-      <c r="B352" s="3" t="n">
-        <v>1.89</v>
+        <v>31818</v>
+      </c>
+      <c r="B352" s="4" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>31881</v>
-      </c>
-      <c r="B353" s="3" t="n">
-        <v>0.71</v>
+        <v>31819</v>
+      </c>
+      <c r="B353" s="4" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>31882</v>
-      </c>
-      <c r="B354" s="3" t="n">
-        <v>1.34</v>
+        <v>31820</v>
+      </c>
+      <c r="B354" s="4" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>31883</v>
-      </c>
-      <c r="B355" s="3" t="n">
-        <v>0.65</v>
+        <v>31821</v>
+      </c>
+      <c r="B355" s="4" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>31884</v>
-      </c>
-      <c r="B356" s="3" t="n">
-        <v>1.33</v>
+        <v>31822</v>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>31885</v>
+        <v>31823</v>
       </c>
       <c r="B357" s="4" t="n">
-        <v>8.9</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>31886</v>
-      </c>
-      <c r="B358" s="4" t="n">
-        <v>7.72</v>
+        <v>31824</v>
+      </c>
+      <c r="B358" s="5" t="n">
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>31887</v>
-      </c>
-      <c r="B359" s="3" t="n">
-        <v>2.66</v>
+        <v>31825</v>
+      </c>
+      <c r="B359" s="4" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>31888</v>
-      </c>
-      <c r="B360" s="3" t="n">
-        <v>1.88</v>
+        <v>31826</v>
+      </c>
+      <c r="B360" s="4" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>31889</v>
-      </c>
-      <c r="B361" s="2" t="n">
-        <v>5.75</v>
+        <v>31827</v>
+      </c>
+      <c r="B361" s="4" t="n">
+        <v>2.11</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>31890</v>
-      </c>
-      <c r="B362" s="3" t="n">
-        <v>1.1</v>
+        <v>31828</v>
+      </c>
+      <c r="B362" s="4" t="n">
+        <v>2.71</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>31891</v>
-      </c>
-      <c r="B363" s="5" t="n">
-        <v>3.97</v>
+        <v>31829</v>
+      </c>
+      <c r="B363" s="4" t="n">
+        <v>2.92</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>31892</v>
-      </c>
-      <c r="B364" s="2" t="n">
-        <v>6.47</v>
+        <v>31830</v>
+      </c>
+      <c r="B364" s="5" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>31893</v>
-      </c>
-      <c r="B365" s="3" t="n">
-        <v>1.07</v>
+        <v>31831</v>
+      </c>
+      <c r="B365" s="4" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>31894</v>
-      </c>
-      <c r="B366" s="3" t="n">
-        <v>1.39</v>
+        <v>31832</v>
+      </c>
+      <c r="B366" s="4" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>31895</v>
+        <v>31833</v>
       </c>
       <c r="B367" s="5" t="n">
-        <v>3.02</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>31896</v>
-      </c>
-      <c r="B368" s="3" t="n">
-        <v>2.05</v>
+        <v>31834</v>
+      </c>
+      <c r="B368" s="5" t="n">
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>31897</v>
-      </c>
-      <c r="B369" s="5" t="n">
-        <v>3.82</v>
+        <v>31835</v>
+      </c>
+      <c r="B369" s="4" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>31898</v>
-      </c>
-      <c r="B370" s="3" t="n">
-        <v>1.96</v>
+        <v>31836</v>
+      </c>
+      <c r="B370" s="4" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>31899</v>
-      </c>
-      <c r="B371" s="3" t="n">
-        <v>2.39</v>
+        <v>31837</v>
+      </c>
+      <c r="B371" s="5" t="n">
+        <v>10.79</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>31900</v>
-      </c>
-      <c r="B372" s="3" t="n">
-        <v>1.63</v>
+        <v>31838</v>
+      </c>
+      <c r="B372" s="2" t="n">
+        <v>3.19</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>31901</v>
-      </c>
-      <c r="B373" s="5" t="n">
-        <v>4.16</v>
+        <v>31839</v>
+      </c>
+      <c r="B373" s="4" t="n">
+        <v>2.72</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>31902</v>
-      </c>
-      <c r="B374" s="3" t="n">
-        <v>2.94</v>
+        <v>31840</v>
+      </c>
+      <c r="B374" s="4" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>31903</v>
-      </c>
-      <c r="B375" s="3" t="n">
-        <v>2.81</v>
+        <v>31841</v>
+      </c>
+      <c r="B375" s="4" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>31904</v>
-      </c>
-      <c r="B376" s="3" t="n">
-        <v>2.36</v>
+        <v>31842</v>
+      </c>
+      <c r="B376" s="4" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>31905</v>
-      </c>
-      <c r="B377" s="3" t="n">
-        <v>1.87</v>
+        <v>31843</v>
+      </c>
+      <c r="B377" s="4" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>31906</v>
-      </c>
-      <c r="B378" s="3" t="n">
-        <v>1.85</v>
+        <v>31844</v>
+      </c>
+      <c r="B378" s="4" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>31907</v>
-      </c>
-      <c r="B379" s="3" t="n">
-        <v>2.47</v>
+        <v>31845</v>
+      </c>
+      <c r="B379" s="4" t="n">
+        <v>2.68</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>31908</v>
-      </c>
-      <c r="B380" s="3" t="n">
-        <v>2.88</v>
+        <v>31846</v>
+      </c>
+      <c r="B380" s="4" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>31909</v>
-      </c>
-      <c r="B381" s="3" t="n">
-        <v>2.22</v>
+        <v>31847</v>
+      </c>
+      <c r="B381" s="5" t="n">
+        <v>11.32</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>31910</v>
+        <v>31848</v>
       </c>
       <c r="B382" s="2" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>31911</v>
-      </c>
-      <c r="B383" s="3" t="n">
-        <v>2.66</v>
+        <v>31849</v>
+      </c>
+      <c r="B383" s="4" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>31912</v>
+        <v>31850</v>
       </c>
       <c r="B384" s="4" t="n">
-        <v>9.050000000000001</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>31913</v>
+        <v>31851</v>
       </c>
       <c r="B385" s="4" t="n">
-        <v>10.71</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>31914</v>
-      </c>
-      <c r="B386" s="4" t="n">
-        <v>7.23</v>
+        <v>31852</v>
+      </c>
+      <c r="B386" s="2" t="n">
+        <v>3.64</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>31915</v>
-      </c>
-      <c r="B387" s="5" t="n">
-        <v>3.85</v>
+        <v>31853</v>
+      </c>
+      <c r="B387" s="4" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>31916</v>
-      </c>
-      <c r="B388" s="3" t="n">
-        <v>0.61</v>
+        <v>31854</v>
+      </c>
+      <c r="B388" s="5" t="n">
+        <v>11.32</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>31917</v>
-      </c>
-      <c r="B389" s="3" t="n">
-        <v>2.04</v>
+        <v>31855</v>
+      </c>
+      <c r="B389" s="4" t="n">
+        <v>2.92</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>31918</v>
-      </c>
-      <c r="B390" s="2" t="n">
-        <v>5.04</v>
+        <v>31856</v>
+      </c>
+      <c r="B390" s="4" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>31919</v>
-      </c>
-      <c r="B391" s="5" t="n">
-        <v>4.19</v>
+        <v>31857</v>
+      </c>
+      <c r="B391" s="4" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>31920</v>
+        <v>31858</v>
       </c>
       <c r="B392" s="4" t="n">
-        <v>16.12</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>31921</v>
+        <v>31859</v>
       </c>
       <c r="B393" s="3" t="n">
-        <v>2.42</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>31922</v>
-      </c>
-      <c r="B394" s="3" t="n">
-        <v>1.04</v>
+        <v>31860</v>
+      </c>
+      <c r="B394" s="4" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>31923</v>
-      </c>
-      <c r="B395" s="5" t="n">
-        <v>4.14</v>
+        <v>31861</v>
+      </c>
+      <c r="B395" s="4" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>31924</v>
-      </c>
-      <c r="B396" s="3" t="n">
-        <v>2.23</v>
+        <v>31862</v>
+      </c>
+      <c r="B396" s="4" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>31925</v>
-      </c>
-      <c r="B397" s="3" t="n">
-        <v>2.78</v>
+        <v>31863</v>
+      </c>
+      <c r="B397" s="4" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>31926</v>
-      </c>
-      <c r="B398" s="3" t="n">
-        <v>2.36</v>
+        <v>31864</v>
+      </c>
+      <c r="B398" s="4" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>31927</v>
-      </c>
-      <c r="B399" s="5" t="n">
-        <v>4.41</v>
+        <v>31865</v>
+      </c>
+      <c r="B399" s="4" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>31928</v>
-      </c>
-      <c r="B400" s="3" t="n">
-        <v>2.85</v>
+        <v>31866</v>
+      </c>
+      <c r="B400" s="4" t="n">
+        <v>2.71</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>31929</v>
-      </c>
-      <c r="B401" s="3" t="n">
-        <v>2.04</v>
+        <v>31867</v>
+      </c>
+      <c r="B401" s="4" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>31930</v>
-      </c>
-      <c r="B402" s="5" t="n">
-        <v>3.87</v>
+        <v>31868</v>
+      </c>
+      <c r="B402" s="4" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>31931</v>
-      </c>
-      <c r="B403" s="3" t="n">
-        <v>1.24</v>
+        <v>31869</v>
+      </c>
+      <c r="B403" s="4" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>31932</v>
-      </c>
-      <c r="B404" s="5" t="n">
-        <v>3.34</v>
+        <v>31870</v>
+      </c>
+      <c r="B404" s="4" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>31933</v>
-      </c>
-      <c r="B405" s="3" t="n">
-        <v>2.82</v>
+        <v>31871</v>
+      </c>
+      <c r="B405" s="4" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>31934</v>
-      </c>
-      <c r="B406" s="3" t="n">
-        <v>1.97</v>
+        <v>31872</v>
+      </c>
+      <c r="B406" s="4" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>31935</v>
-      </c>
-      <c r="B407" s="3" t="n">
-        <v>1.91</v>
+        <v>31873</v>
+      </c>
+      <c r="B407" s="4" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>31936</v>
-      </c>
-      <c r="B408" s="5" t="n">
-        <v>3.88</v>
+        <v>31874</v>
+      </c>
+      <c r="B408" s="2" t="n">
+        <v>3.32</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>31937</v>
-      </c>
-      <c r="B409" s="3" t="n">
-        <v>1.93</v>
+        <v>31875</v>
+      </c>
+      <c r="B409" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>31938</v>
-      </c>
-      <c r="B410" s="3" t="n">
-        <v>2.26</v>
+        <v>31876</v>
+      </c>
+      <c r="B410" s="4" t="n">
+        <v>1.56</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>31939</v>
-      </c>
-      <c r="B411" s="3" t="n">
-        <v>2.15</v>
+        <v>31877</v>
+      </c>
+      <c r="B411" s="2" t="n">
+        <v>3.17</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>31940</v>
-      </c>
-      <c r="B412" s="3" t="n">
-        <v>2.84</v>
+        <v>31878</v>
+      </c>
+      <c r="B412" s="4" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>31941</v>
-      </c>
-      <c r="B413" s="3" t="n">
-        <v>1.35</v>
+        <v>31879</v>
+      </c>
+      <c r="B413" s="4" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>31942</v>
-      </c>
-      <c r="B414" s="3" t="n">
-        <v>2.07</v>
+        <v>31880</v>
+      </c>
+      <c r="B414" s="4" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>31943</v>
-      </c>
-      <c r="B415" s="3" t="n">
-        <v>1.69</v>
+        <v>31881</v>
+      </c>
+      <c r="B415" s="4" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>31944</v>
-      </c>
-      <c r="B416" s="3" t="n">
-        <v>0.88</v>
+        <v>31882</v>
+      </c>
+      <c r="B416" s="4" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>31945</v>
-      </c>
-      <c r="B417" s="3" t="n">
-        <v>2.08</v>
+        <v>31883</v>
+      </c>
+      <c r="B417" s="4" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>31946</v>
+        <v>31884</v>
       </c>
       <c r="B418" s="4" t="n">
-        <v>7.54</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>31947</v>
-      </c>
-      <c r="B419" s="3" t="n">
-        <v>1.3</v>
+        <v>31885</v>
+      </c>
+      <c r="B419" s="5" t="n">
+        <v>8.9</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>31948</v>
-      </c>
-      <c r="B420" s="3" t="n">
-        <v>2.27</v>
+        <v>31886</v>
+      </c>
+      <c r="B420" s="5" t="n">
+        <v>7.72</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>31949</v>
-      </c>
-      <c r="B421" s="3" t="n">
-        <v>2.07</v>
+        <v>31887</v>
+      </c>
+      <c r="B421" s="4" t="n">
+        <v>2.66</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>31950</v>
+        <v>31888</v>
       </c>
       <c r="B422" s="4" t="n">
-        <v>7.8</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>31951</v>
+        <v>31889</v>
       </c>
       <c r="B423" s="3" t="n">
-        <v>0.91</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>31952</v>
-      </c>
-      <c r="B424" s="3" t="n">
-        <v>1.5</v>
+        <v>31890</v>
+      </c>
+      <c r="B424" s="4" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>31953</v>
-      </c>
-      <c r="B425" s="5" t="n">
-        <v>3.4</v>
+        <v>31891</v>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>3.97</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>31954</v>
+        <v>31892</v>
       </c>
       <c r="B426" s="3" t="n">
-        <v>0.92</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>31955</v>
-      </c>
-      <c r="B427" s="3" t="n">
-        <v>1.71</v>
+        <v>31893</v>
+      </c>
+      <c r="B427" s="4" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>31956</v>
+        <v>31894</v>
       </c>
       <c r="B428" s="4" t="n">
-        <v>7.55</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>31957</v>
-      </c>
-      <c r="B429" s="3" t="n">
-        <v>1.14</v>
+        <v>31895</v>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>3.02</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>31958</v>
-      </c>
-      <c r="B430" s="3" t="n">
-        <v>0.82</v>
+        <v>31896</v>
+      </c>
+      <c r="B430" s="4" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>31959</v>
-      </c>
-      <c r="B431" s="3" t="n">
-        <v>1.53</v>
+        <v>31897</v>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>3.82</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>31960</v>
-      </c>
-      <c r="B432" s="3" t="n">
-        <v>1.83</v>
+        <v>31898</v>
+      </c>
+      <c r="B432" s="4" t="n">
+        <v>1.96</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>31961</v>
-      </c>
-      <c r="B433" s="3" t="n">
-        <v>2.42</v>
+        <v>31899</v>
+      </c>
+      <c r="B433" s="4" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>31962</v>
-      </c>
-      <c r="B434" s="3" t="n">
-        <v>1.67</v>
+        <v>31900</v>
+      </c>
+      <c r="B434" s="4" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>31963</v>
-      </c>
-      <c r="B435" s="3" t="n">
-        <v>2.53</v>
+        <v>31901</v>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>4.16</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>31964</v>
-      </c>
-      <c r="B436" s="3" t="n">
-        <v>2.33</v>
+        <v>31902</v>
+      </c>
+      <c r="B436" s="4" t="n">
+        <v>2.94</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>31965</v>
-      </c>
-      <c r="B437" s="3" t="n">
-        <v>2.64</v>
+        <v>31903</v>
+      </c>
+      <c r="B437" s="4" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>31966</v>
-      </c>
-      <c r="B438" s="3" t="n">
-        <v>2.09</v>
+        <v>31904</v>
+      </c>
+      <c r="B438" s="4" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>31967</v>
-      </c>
-      <c r="B439" s="3" t="n">
-        <v>2.41</v>
+        <v>31905</v>
+      </c>
+      <c r="B439" s="4" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>31968</v>
-      </c>
-      <c r="B440" s="5" t="n">
-        <v>3.46</v>
+        <v>31906</v>
+      </c>
+      <c r="B440" s="4" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>31969</v>
-      </c>
-      <c r="B441" s="3" t="n">
-        <v>2.79</v>
+        <v>31907</v>
+      </c>
+      <c r="B441" s="4" t="n">
+        <v>2.47</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>31970</v>
-      </c>
-      <c r="B442" s="3" t="n">
-        <v>1.92</v>
+        <v>31908</v>
+      </c>
+      <c r="B442" s="4" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>31971</v>
-      </c>
-      <c r="B443" s="3" t="n">
-        <v>2.74</v>
+        <v>31909</v>
+      </c>
+      <c r="B443" s="4" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>31972</v>
+        <v>31910</v>
       </c>
       <c r="B444" s="3" t="n">
-        <v>1.91</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>31973</v>
-      </c>
-      <c r="B445" s="3" t="n">
-        <v>2.1</v>
+        <v>31911</v>
+      </c>
+      <c r="B445" s="4" t="n">
+        <v>2.66</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>31974</v>
-      </c>
-      <c r="B446" s="3" t="n">
-        <v>2.86</v>
+        <v>31912</v>
+      </c>
+      <c r="B446" s="5" t="n">
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>31975</v>
+        <v>31913</v>
       </c>
       <c r="B447" s="5" t="n">
-        <v>3.43</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>31976</v>
-      </c>
-      <c r="B448" s="3" t="n">
-        <v>1.64</v>
+        <v>31914</v>
+      </c>
+      <c r="B448" s="5" t="n">
+        <v>7.23</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>31977</v>
-      </c>
-      <c r="B449" s="3" t="n">
-        <v>2.6</v>
+        <v>31915</v>
+      </c>
+      <c r="B449" s="2" t="n">
+        <v>3.85</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>31978</v>
-      </c>
-      <c r="B450" s="3" t="n">
-        <v>1.38</v>
+        <v>31916</v>
+      </c>
+      <c r="B450" s="4" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>31979</v>
-      </c>
-      <c r="B451" s="3" t="n">
-        <v>1.21</v>
+        <v>31917</v>
+      </c>
+      <c r="B451" s="4" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>31980</v>
+        <v>31918</v>
       </c>
       <c r="B452" s="3" t="n">
-        <v>1.47</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>31981</v>
-      </c>
-      <c r="B453" s="5" t="n">
-        <v>4.78</v>
+        <v>31919</v>
+      </c>
+      <c r="B453" s="2" t="n">
+        <v>4.19</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>31982</v>
-      </c>
-      <c r="B454" s="4" t="n">
-        <v>11.24</v>
+        <v>31920</v>
+      </c>
+      <c r="B454" s="5" t="n">
+        <v>16.12</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>31983</v>
-      </c>
-      <c r="B455" s="3" t="n">
-        <v>1.51</v>
+        <v>31921</v>
+      </c>
+      <c r="B455" s="4" t="n">
+        <v>2.42</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>31984</v>
-      </c>
-      <c r="B456" s="3" t="n">
-        <v>1.71</v>
+        <v>31922</v>
+      </c>
+      <c r="B456" s="4" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>31985</v>
-      </c>
-      <c r="B457" s="3" t="n">
-        <v>2.5</v>
+        <v>31923</v>
+      </c>
+      <c r="B457" s="2" t="n">
+        <v>4.14</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>31986</v>
+        <v>31924</v>
       </c>
       <c r="B458" s="4" t="n">
-        <v>7.52</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>31987</v>
-      </c>
-      <c r="B459" s="5" t="n">
-        <v>3.31</v>
+        <v>31925</v>
+      </c>
+      <c r="B459" s="4" t="n">
+        <v>2.78</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>31988</v>
-      </c>
-      <c r="B460" s="3" t="n">
-        <v>2.04</v>
+        <v>31926</v>
+      </c>
+      <c r="B460" s="4" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>31989</v>
-      </c>
-      <c r="B461" s="3" t="n">
-        <v>2.76</v>
+        <v>31927</v>
+      </c>
+      <c r="B461" s="2" t="n">
+        <v>4.41</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>31990</v>
-      </c>
-      <c r="B462" s="3" t="n">
-        <v>1.87</v>
+        <v>31928</v>
+      </c>
+      <c r="B462" s="4" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>31991</v>
-      </c>
-      <c r="B463" s="3" t="n">
-        <v>1.26</v>
+        <v>31929</v>
+      </c>
+      <c r="B463" s="4" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>31992</v>
-      </c>
-      <c r="B464" s="3" t="n">
-        <v>1.46</v>
+        <v>31930</v>
+      </c>
+      <c r="B464" s="2" t="n">
+        <v>3.87</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
+        <v>31931</v>
+      </c>
+      <c r="B465" s="4" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>31932</v>
+      </c>
+      <c r="B466" s="2" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>31933</v>
+      </c>
+      <c r="B467" s="4" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>31934</v>
+      </c>
+      <c r="B468" s="4" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>31935</v>
+      </c>
+      <c r="B469" s="4" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>31936</v>
+      </c>
+      <c r="B470" s="2" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>31937</v>
+      </c>
+      <c r="B471" s="4" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>31938</v>
+      </c>
+      <c r="B472" s="4" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>31939</v>
+      </c>
+      <c r="B473" s="4" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>31940</v>
+      </c>
+      <c r="B474" s="4" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>31941</v>
+      </c>
+      <c r="B475" s="4" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>31942</v>
+      </c>
+      <c r="B476" s="4" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>31943</v>
+      </c>
+      <c r="B477" s="4" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>31944</v>
+      </c>
+      <c r="B478" s="4" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>31945</v>
+      </c>
+      <c r="B479" s="4" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>31946</v>
+      </c>
+      <c r="B480" s="5" t="n">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>31947</v>
+      </c>
+      <c r="B481" s="4" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>31948</v>
+      </c>
+      <c r="B482" s="4" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>31949</v>
+      </c>
+      <c r="B483" s="4" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>31950</v>
+      </c>
+      <c r="B484" s="5" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>31951</v>
+      </c>
+      <c r="B485" s="4" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>31952</v>
+      </c>
+      <c r="B486" s="4" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>31953</v>
+      </c>
+      <c r="B487" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>31954</v>
+      </c>
+      <c r="B488" s="4" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>31955</v>
+      </c>
+      <c r="B489" s="4" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>31956</v>
+      </c>
+      <c r="B490" s="5" t="n">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>31957</v>
+      </c>
+      <c r="B491" s="4" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>31958</v>
+      </c>
+      <c r="B492" s="4" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>31959</v>
+      </c>
+      <c r="B493" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>31960</v>
+      </c>
+      <c r="B494" s="4" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>31961</v>
+      </c>
+      <c r="B495" s="4" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>31962</v>
+      </c>
+      <c r="B496" s="4" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>31963</v>
+      </c>
+      <c r="B497" s="4" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>31964</v>
+      </c>
+      <c r="B498" s="4" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>31965</v>
+      </c>
+      <c r="B499" s="4" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>31966</v>
+      </c>
+      <c r="B500" s="4" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>31967</v>
+      </c>
+      <c r="B501" s="4" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>31968</v>
+      </c>
+      <c r="B502" s="2" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>31969</v>
+      </c>
+      <c r="B503" s="4" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>31970</v>
+      </c>
+      <c r="B504" s="4" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>31971</v>
+      </c>
+      <c r="B505" s="4" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>31972</v>
+      </c>
+      <c r="B506" s="4" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>31973</v>
+      </c>
+      <c r="B507" s="4" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>31974</v>
+      </c>
+      <c r="B508" s="4" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>31975</v>
+      </c>
+      <c r="B509" s="2" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>31976</v>
+      </c>
+      <c r="B510" s="4" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>31977</v>
+      </c>
+      <c r="B511" s="4" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>31978</v>
+      </c>
+      <c r="B512" s="4" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>31979</v>
+      </c>
+      <c r="B513" s="4" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>31980</v>
+      </c>
+      <c r="B514" s="4" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>31981</v>
+      </c>
+      <c r="B515" s="2" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>31982</v>
+      </c>
+      <c r="B516" s="5" t="n">
+        <v>11.24</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>31983</v>
+      </c>
+      <c r="B517" s="4" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>31984</v>
+      </c>
+      <c r="B518" s="4" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>31985</v>
+      </c>
+      <c r="B519" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>31986</v>
+      </c>
+      <c r="B520" s="5" t="n">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>31987</v>
+      </c>
+      <c r="B521" s="2" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>31988</v>
+      </c>
+      <c r="B522" s="4" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>31989</v>
+      </c>
+      <c r="B523" s="4" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>31990</v>
+      </c>
+      <c r="B524" s="4" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>31991</v>
+      </c>
+      <c r="B525" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>31992</v>
+      </c>
+      <c r="B526" s="4" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
         <v>31993</v>
       </c>
-      <c r="B465" s="2" t="n">
+      <c r="B527" s="3" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>31994</v>
+      </c>
+      <c r="B528" s="2" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>31995</v>
+      </c>
+      <c r="B529" s="2" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>31996</v>
+      </c>
+      <c r="B530" s="4" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>31997</v>
+      </c>
+      <c r="B531" s="4" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>31998</v>
+      </c>
+      <c r="B532" s="2" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>31999</v>
+      </c>
+      <c r="B533" s="4" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>32000</v>
+      </c>
+      <c r="B534" s="4" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>32001</v>
+      </c>
+      <c r="B535" s="2" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>32002</v>
+      </c>
+      <c r="B536" s="2" t="n">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>32003</v>
+      </c>
+      <c r="B537" s="4" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>32004</v>
+      </c>
+      <c r="B538" s="4" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>32005</v>
+      </c>
+      <c r="B539" s="4" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>32006</v>
+      </c>
+      <c r="B540" s="3" t="n">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>32007</v>
+      </c>
+      <c r="B541" s="4" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>32008</v>
+      </c>
+      <c r="B542" s="4" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>32009</v>
+      </c>
+      <c r="B543" s="4" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>32010</v>
+      </c>
+      <c r="B544" s="4" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>32011</v>
+      </c>
+      <c r="B545" s="4" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>32012</v>
+      </c>
+      <c r="B546" s="4" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>32013</v>
+      </c>
+      <c r="B547" s="4" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>32014</v>
+      </c>
+      <c r="B548" s="3" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>32015</v>
+      </c>
+      <c r="B549" s="4" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>32016</v>
+      </c>
+      <c r="B550" s="4" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>32017</v>
+      </c>
+      <c r="B551" s="4" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>32018</v>
+      </c>
+      <c r="B552" s="2" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>32019</v>
+      </c>
+      <c r="B553" s="4" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>32020</v>
+      </c>
+      <c r="B554" s="4" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>32021</v>
+      </c>
+      <c r="B555" s="4" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>32022</v>
+      </c>
+      <c r="B556" s="4" t="n">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>32023</v>
+      </c>
+      <c r="B557" s="4" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>32024</v>
+      </c>
+      <c r="B558" s="4" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>32025</v>
+      </c>
+      <c r="B559" s="3" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>32026</v>
+      </c>
+      <c r="B560" s="4" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>32027</v>
+      </c>
+      <c r="B561" s="4" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>32028</v>
+      </c>
+      <c r="B562" s="4" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>32029</v>
+      </c>
+      <c r="B563" s="4" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>32030</v>
+      </c>
+      <c r="B564" s="4" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>32031</v>
+      </c>
+      <c r="B565" s="4" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>32032</v>
+      </c>
+      <c r="B566" s="2" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>32033</v>
+      </c>
+      <c r="B567" s="4" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>32034</v>
+      </c>
+      <c r="B568" s="4" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>32035</v>
+      </c>
+      <c r="B569" s="4" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>32036</v>
+      </c>
+      <c r="B570" s="4" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>32037</v>
+      </c>
+      <c r="B571" s="4" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>32038</v>
+      </c>
+      <c r="B572" s="4" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>32039</v>
+      </c>
+      <c r="B573" s="4" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>32040</v>
+      </c>
+      <c r="B574" s="3" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>32041</v>
+      </c>
+      <c r="B575" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>32042</v>
+      </c>
+      <c r="B576" s="4" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>32043</v>
+      </c>
+      <c r="B577" s="4" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>32044</v>
+      </c>
+      <c r="B578" s="4" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>32045</v>
+      </c>
+      <c r="B579" s="4" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>32046</v>
+      </c>
+      <c r="B580" s="4" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>32047</v>
+      </c>
+      <c r="B581" s="4" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>32048</v>
+      </c>
+      <c r="B582" s="4" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>32049</v>
+      </c>
+      <c r="B583" s="4" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>32050</v>
+      </c>
+      <c r="B584" s="4" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>32051</v>
+      </c>
+      <c r="B585" s="4" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>32052</v>
+      </c>
+      <c r="B586" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>32053</v>
+      </c>
+      <c r="B587" s="4" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>32054</v>
+      </c>
+      <c r="B588" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>32055</v>
+      </c>
+      <c r="B589" s="2" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>32056</v>
+      </c>
+      <c r="B590" s="4" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>32057</v>
+      </c>
+      <c r="B591" s="2" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>32058</v>
+      </c>
+      <c r="B592" s="4" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>32059</v>
+      </c>
+      <c r="B593" s="4" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>32060</v>
+      </c>
+      <c r="B594" s="4" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>32061</v>
+      </c>
+      <c r="B595" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>32062</v>
+      </c>
+      <c r="B596" s="5" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>32063</v>
+      </c>
+      <c r="B597" s="4" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>32064</v>
+      </c>
+      <c r="B598" s="4" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>32065</v>
+      </c>
+      <c r="B599" s="2" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>32066</v>
+      </c>
+      <c r="B600" s="4" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>32067</v>
+      </c>
+      <c r="B601" s="4" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>32068</v>
+      </c>
+      <c r="B602" s="4" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>32069</v>
+      </c>
+      <c r="B603" s="4" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>32070</v>
+      </c>
+      <c r="B604" s="4" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>32071</v>
+      </c>
+      <c r="B605" s="4" t="n">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>32072</v>
+      </c>
+      <c r="B606" s="4" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>32073</v>
+      </c>
+      <c r="B607" s="4" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>32074</v>
+      </c>
+      <c r="B608" s="4" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>32075</v>
+      </c>
+      <c r="B609" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>32076</v>
+      </c>
+      <c r="B610" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>32077</v>
+      </c>
+      <c r="B611" s="4" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>32078</v>
+      </c>
+      <c r="B612" s="4" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>32079</v>
+      </c>
+      <c r="B613" s="4" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>32080</v>
+      </c>
+      <c r="B614" s="4" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>32081</v>
+      </c>
+      <c r="B615" s="4" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>32082</v>
+      </c>
+      <c r="B616" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>32083</v>
+      </c>
+      <c r="B617" s="4" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>32084</v>
+      </c>
+      <c r="B618" s="4" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>32085</v>
+      </c>
+      <c r="B619" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>32086</v>
+      </c>
+      <c r="B620" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>32087</v>
+      </c>
+      <c r="B621" s="4" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>32088</v>
+      </c>
+      <c r="B622" s="4" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>32089</v>
+      </c>
+      <c r="B623" s="4" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>32090</v>
+      </c>
+      <c r="B624" s="4" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>32091</v>
+      </c>
+      <c r="B625" s="4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>32092</v>
+      </c>
+      <c r="B626" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>32093</v>
+      </c>
+      <c r="B627" s="4" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>32094</v>
+      </c>
+      <c r="B628" s="4" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>32095</v>
+      </c>
+      <c r="B629" s="4" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>32096</v>
+      </c>
+      <c r="B630" s="4" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>32097</v>
+      </c>
+      <c r="B631" s="2" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>32098</v>
+      </c>
+      <c r="B632" s="4" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>32099</v>
+      </c>
+      <c r="B633" s="4" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>32100</v>
+      </c>
+      <c r="B634" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>32101</v>
+      </c>
+      <c r="B635" s="4" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>32102</v>
+      </c>
+      <c r="B636" s="4" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>32103</v>
+      </c>
+      <c r="B637" s="4" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>32104</v>
+      </c>
+      <c r="B638" s="2" t="n">
+        <v>4.81</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>32105</v>
+      </c>
+      <c r="B639" s="4" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>32106</v>
+      </c>
+      <c r="B640" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>32107</v>
+      </c>
+      <c r="B641" s="4" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>32108</v>
+      </c>
+      <c r="B642" s="4" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>32109</v>
+      </c>
+      <c r="B643" s="2" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>32110</v>
+      </c>
+      <c r="B644" s="4" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>32111</v>
+      </c>
+      <c r="B645" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>32112</v>
+      </c>
+      <c r="B646" s="2" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>32113</v>
+      </c>
+      <c r="B647" s="4" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>32114</v>
+      </c>
+      <c r="B648" s="4" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>32115</v>
+      </c>
+      <c r="B649" s="4" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>32116</v>
+      </c>
+      <c r="B650" s="4" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>32117</v>
+      </c>
+      <c r="B651" s="4" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>32118</v>
+      </c>
+      <c r="B652" s="4" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>32119</v>
+      </c>
+      <c r="B653" s="4" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>32120</v>
+      </c>
+      <c r="B654" s="2" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>32121</v>
+      </c>
+      <c r="B655" s="4" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>32122</v>
+      </c>
+      <c r="B656" s="2" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>32123</v>
+      </c>
+      <c r="B657" s="4" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>32124</v>
+      </c>
+      <c r="B658" s="4" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>32125</v>
+      </c>
+      <c r="B659" s="4" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>32126</v>
+      </c>
+      <c r="B660" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>32127</v>
+      </c>
+      <c r="B661" s="5" t="n">
+        <v>77.23999999999999</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>32128</v>
+      </c>
+      <c r="B662" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>32129</v>
+      </c>
+      <c r="B663" s="4" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>32130</v>
+      </c>
+      <c r="B664" s="4" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>32131</v>
+      </c>
+      <c r="B665" s="4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>32132</v>
+      </c>
+      <c r="B666" s="4" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>32133</v>
+      </c>
+      <c r="B667" s="2" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>32134</v>
+      </c>
+      <c r="B668" s="2" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>32135</v>
+      </c>
+      <c r="B669" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>32136</v>
+      </c>
+      <c r="B670" s="2" t="n">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>32137</v>
+      </c>
+      <c r="B671" s="4" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>32138</v>
+      </c>
+      <c r="B672" s="4" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>32139</v>
+      </c>
+      <c r="B673" s="4" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B674" s="2" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>32141</v>
+      </c>
+      <c r="B675" s="2" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>32142</v>
+      </c>
+      <c r="B676" s="4" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>32143</v>
+      </c>
+      <c r="B677" s="4" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>32144</v>
+      </c>
+      <c r="B678" s="2" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>32145</v>
+      </c>
+      <c r="B679" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>32146</v>
+      </c>
+      <c r="B680" s="4" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>32147</v>
+      </c>
+      <c r="B681" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>32148</v>
+      </c>
+      <c r="B682" s="4" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>32149</v>
+      </c>
+      <c r="B683" s="4" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>32150</v>
+      </c>
+      <c r="B684" s="4" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>32151</v>
+      </c>
+      <c r="B685" s="2" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>32152</v>
+      </c>
+      <c r="B686" s="4" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>32153</v>
+      </c>
+      <c r="B687" s="4" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>32154</v>
+      </c>
+      <c r="B688" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>32155</v>
+      </c>
+      <c r="B689" s="4" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>32156</v>
+      </c>
+      <c r="B690" s="4" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>32157</v>
+      </c>
+      <c r="B691" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>32158</v>
+      </c>
+      <c r="B692" s="4" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>32159</v>
+      </c>
+      <c r="B693" s="2" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>32160</v>
+      </c>
+      <c r="B694" s="4" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>32161</v>
+      </c>
+      <c r="B695" s="4" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>32162</v>
+      </c>
+      <c r="B696" s="4" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>32163</v>
+      </c>
+      <c r="B697" s="4" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>32164</v>
+      </c>
+      <c r="B698" s="4" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>32165</v>
+      </c>
+      <c r="B699" s="4" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>32166</v>
+      </c>
+      <c r="B700" s="4" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>32167</v>
+      </c>
+      <c r="B701" s="4" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>32168</v>
+      </c>
+      <c r="B702" s="4" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>32169</v>
+      </c>
+      <c r="B703" s="4" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>32170</v>
+      </c>
+      <c r="B704" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>32171</v>
+      </c>
+      <c r="B705" s="4" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>32172</v>
+      </c>
+      <c r="B706" s="4" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>32173</v>
+      </c>
+      <c r="B707" s="4" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>32174</v>
+      </c>
+      <c r="B708" s="4" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>32175</v>
+      </c>
+      <c r="B709" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>32176</v>
+      </c>
+      <c r="B710" s="2" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>32177</v>
+      </c>
+      <c r="B711" s="4" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>32178</v>
+      </c>
+      <c r="B712" s="4" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>32179</v>
+      </c>
+      <c r="B713" s="4" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>32180</v>
+      </c>
+      <c r="B714" s="2" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>32181</v>
+      </c>
+      <c r="B715" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>32182</v>
+      </c>
+      <c r="B716" s="4" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>32183</v>
+      </c>
+      <c r="B717" s="4" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>32184</v>
+      </c>
+      <c r="B718" s="2" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>32185</v>
+      </c>
+      <c r="B719" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>32186</v>
+      </c>
+      <c r="B720" s="4" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>32187</v>
+      </c>
+      <c r="B721" s="5" t="n">
+        <v>15.37</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>32188</v>
+      </c>
+      <c r="B722" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>32189</v>
+      </c>
+      <c r="B723" s="4" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>32190</v>
+      </c>
+      <c r="B724" s="4" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>32191</v>
+      </c>
+      <c r="B725" s="4" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>32192</v>
+      </c>
+      <c r="B726" s="4" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>32193</v>
+      </c>
+      <c r="B727" s="4" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>32194</v>
+      </c>
+      <c r="B728" s="5" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>32195</v>
+      </c>
+      <c r="B729" s="4" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>32196</v>
+      </c>
+      <c r="B730" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>32197</v>
+      </c>
+      <c r="B731" s="4" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>32198</v>
+      </c>
+      <c r="B732" s="4" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>32199</v>
+      </c>
+      <c r="B733" s="4" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>32200</v>
+      </c>
+      <c r="B734" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>32201</v>
+      </c>
+      <c r="B735" s="3" t="n">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>32202</v>
+      </c>
+      <c r="B736" s="4" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>32203</v>
+      </c>
+      <c r="B737" s="2" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>32204</v>
+      </c>
+      <c r="B738" s="4" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>32207</v>
+      </c>
+      <c r="B739" s="4" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>32208</v>
+      </c>
+      <c r="B740" s="2" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>32209</v>
+      </c>
+      <c r="B741" s="4" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>32210</v>
+      </c>
+      <c r="B742" s="2" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>32211</v>
+      </c>
+      <c r="B743" s="4" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>32212</v>
+      </c>
+      <c r="B744" s="4" t="n">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>32213</v>
+      </c>
+      <c r="B745" s="4" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>32214</v>
+      </c>
+      <c r="B746" s="4" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>32215</v>
+      </c>
+      <c r="B747" s="4" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>32216</v>
+      </c>
+      <c r="B748" s="4" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>32217</v>
+      </c>
+      <c r="B749" s="4" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>32218</v>
+      </c>
+      <c r="B750" s="4" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>32219</v>
+      </c>
+      <c r="B751" s="4" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>32220</v>
+      </c>
+      <c r="B752" s="2" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>32221</v>
+      </c>
+      <c r="B753" s="4" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>32222</v>
+      </c>
+      <c r="B754" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>32223</v>
+      </c>
+      <c r="B755" s="2" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>32224</v>
+      </c>
+      <c r="B756" s="4" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>32225</v>
+      </c>
+      <c r="B757" s="4" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>32226</v>
+      </c>
+      <c r="B758" s="4" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>32227</v>
+      </c>
+      <c r="B759" s="4" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>32228</v>
+      </c>
+      <c r="B760" s="4" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>32229</v>
+      </c>
+      <c r="B761" s="4" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>32230</v>
+      </c>
+      <c r="B762" s="4" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>32231</v>
+      </c>
+      <c r="B763" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>32232</v>
+      </c>
+      <c r="B764" s="4" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>32233</v>
+      </c>
+      <c r="B765" s="2" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>32234</v>
+      </c>
+      <c r="B766" s="4" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>32235</v>
+      </c>
+      <c r="B767" s="4" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>32236</v>
+      </c>
+      <c r="B768" s="4" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>32237</v>
+      </c>
+      <c r="B769" s="4" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>32238</v>
+      </c>
+      <c r="B770" s="4" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>32239</v>
+      </c>
+      <c r="B771" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>32240</v>
+      </c>
+      <c r="B772" s="4" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>32241</v>
+      </c>
+      <c r="B773" s="4" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>32242</v>
+      </c>
+      <c r="B774" s="4" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>32243</v>
+      </c>
+      <c r="B775" s="4" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>32244</v>
+      </c>
+      <c r="B776" s="4" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>32245</v>
+      </c>
+      <c r="B777" s="4" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>32246</v>
+      </c>
+      <c r="B778" s="4" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>32247</v>
+      </c>
+      <c r="B779" s="4" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>32248</v>
+      </c>
+      <c r="B780" s="4" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>32249</v>
+      </c>
+      <c r="B781" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>32250</v>
+      </c>
+      <c r="B782" s="4" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>32251</v>
+      </c>
+      <c r="B783" s="4" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>32252</v>
+      </c>
+      <c r="B784" s="4" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>32253</v>
+      </c>
+      <c r="B785" s="4" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>32254</v>
+      </c>
+      <c r="B786" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>32255</v>
+      </c>
+      <c r="B787" s="4" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>32256</v>
+      </c>
+      <c r="B788" s="4" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>32257</v>
+      </c>
+      <c r="B789" s="4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>32258</v>
+      </c>
+      <c r="B790" s="4" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>32259</v>
+      </c>
+      <c r="B791" s="3" t="n">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>32260</v>
+      </c>
+      <c r="B792" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>32261</v>
+      </c>
+      <c r="B793" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>32262</v>
+      </c>
+      <c r="B794" s="4" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>32263</v>
+      </c>
+      <c r="B795" s="4" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>32264</v>
+      </c>
+      <c r="B796" s="4" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>32265</v>
+      </c>
+      <c r="B797" s="4" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>32266</v>
+      </c>
+      <c r="B798" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>32267</v>
+      </c>
+      <c r="B799" s="2" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>32268</v>
+      </c>
+      <c r="B800" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>32269</v>
+      </c>
+      <c r="B801" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>32270</v>
+      </c>
+      <c r="B802" s="4" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>32271</v>
+      </c>
+      <c r="B803" s="4" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>32272</v>
+      </c>
+      <c r="B804" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>32273</v>
+      </c>
+      <c r="B805" s="4" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>32274</v>
+      </c>
+      <c r="B806" s="4" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>32275</v>
+      </c>
+      <c r="B807" s="4" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>32276</v>
+      </c>
+      <c r="B808" s="4" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>32277</v>
+      </c>
+      <c r="B809" s="4" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>32278</v>
+      </c>
+      <c r="B810" s="4" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>32279</v>
+      </c>
+      <c r="B811" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>32280</v>
+      </c>
+      <c r="B812" s="4" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>32281</v>
+      </c>
+      <c r="B813" s="4" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>32282</v>
+      </c>
+      <c r="B814" s="4" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>32283</v>
+      </c>
+      <c r="B815" s="4" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>32284</v>
+      </c>
+      <c r="B816" s="4" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>32285</v>
+      </c>
+      <c r="B817" s="4" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>32286</v>
+      </c>
+      <c r="B818" s="2" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>32287</v>
+      </c>
+      <c r="B819" s="4" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>32288</v>
+      </c>
+      <c r="B820" s="2" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>32289</v>
+      </c>
+      <c r="B821" s="4" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>32290</v>
+      </c>
+      <c r="B822" s="4" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>32291</v>
+      </c>
+      <c r="B823" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>32292</v>
+      </c>
+      <c r="B824" s="4" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>32293</v>
+      </c>
+      <c r="B825" s="4" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>32294</v>
+      </c>
+      <c r="B826" s="4" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>32295</v>
+      </c>
+      <c r="B827" s="4" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>32296</v>
+      </c>
+      <c r="B828" s="4" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>32297</v>
+      </c>
+      <c r="B829" s="4" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>32298</v>
+      </c>
+      <c r="B830" s="4" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>32299</v>
+      </c>
+      <c r="B831" s="4" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>32300</v>
+      </c>
+      <c r="B832" s="4" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>32301</v>
+      </c>
+      <c r="B833" s="4" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>32302</v>
+      </c>
+      <c r="B834" s="4" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>32303</v>
+      </c>
+      <c r="B835" s="4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>32304</v>
+      </c>
+      <c r="B836" s="4" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>32305</v>
+      </c>
+      <c r="B837" s="3" t="n">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>32306</v>
+      </c>
+      <c r="B838" s="4" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>32308</v>
+      </c>
+      <c r="B839" s="4" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>32309</v>
+      </c>
+      <c r="B840" s="4" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>32310</v>
+      </c>
+      <c r="B841" s="4" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>32311</v>
+      </c>
+      <c r="B842" s="4" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>32313</v>
+      </c>
+      <c r="B843" s="4" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>32314</v>
+      </c>
+      <c r="B844" s="4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>32315</v>
+      </c>
+      <c r="B845" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>32316</v>
+      </c>
+      <c r="B846" s="4" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>32317</v>
+      </c>
+      <c r="B847" s="4" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>32318</v>
+      </c>
+      <c r="B848" s="4" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>32319</v>
+      </c>
+      <c r="B849" s="4" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>32320</v>
+      </c>
+      <c r="B850" s="4" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>32321</v>
+      </c>
+      <c r="B851" s="4" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>32322</v>
+      </c>
+      <c r="B852" s="4" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>32323</v>
+      </c>
+      <c r="B853" s="4" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>32324</v>
+      </c>
+      <c r="B854" s="4" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>32325</v>
+      </c>
+      <c r="B855" s="4" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>32326</v>
+      </c>
+      <c r="B856" s="4" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>32327</v>
+      </c>
+      <c r="B857" s="4" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>32328</v>
+      </c>
+      <c r="B858" s="2" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>32329</v>
+      </c>
+      <c r="B859" s="4" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>32330</v>
+      </c>
+      <c r="B860" s="4" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>32331</v>
+      </c>
+      <c r="B861" s="4" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>32332</v>
+      </c>
+      <c r="B862" s="4" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>32333</v>
+      </c>
+      <c r="B863" s="4" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>32334</v>
+      </c>
+      <c r="B864" s="4" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>32335</v>
+      </c>
+      <c r="B865" s="4" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>32336</v>
+      </c>
+      <c r="B866" s="4" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>32337</v>
+      </c>
+      <c r="B867" s="4" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>32338</v>
+      </c>
+      <c r="B868" s="4" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>32339</v>
+      </c>
+      <c r="B869" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>32340</v>
+      </c>
+      <c r="B870" s="4" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>32341</v>
+      </c>
+      <c r="B871" s="4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>32342</v>
+      </c>
+      <c r="B872" s="4" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>32343</v>
+      </c>
+      <c r="B873" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>32344</v>
+      </c>
+      <c r="B874" s="4" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>32345</v>
+      </c>
+      <c r="B875" s="4" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>32346</v>
+      </c>
+      <c r="B876" s="4" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>32347</v>
+      </c>
+      <c r="B877" s="4" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>32348</v>
+      </c>
+      <c r="B878" s="2" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>32349</v>
+      </c>
+      <c r="B879" s="4" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>32350</v>
+      </c>
+      <c r="B880" s="4" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>32351</v>
+      </c>
+      <c r="B881" s="4" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>32352</v>
+      </c>
+      <c r="B882" s="4" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>32353</v>
+      </c>
+      <c r="B883" s="4" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>32354</v>
+      </c>
+      <c r="B884" s="4" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>32355</v>
+      </c>
+      <c r="B885" s="4" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>32356</v>
+      </c>
+      <c r="B886" s="4" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>32357</v>
+      </c>
+      <c r="B887" s="4" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>32358</v>
+      </c>
+      <c r="B888" s="4" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>32359</v>
+      </c>
+      <c r="B889" s="4" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>32360</v>
+      </c>
+      <c r="B890" s="4" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>32361</v>
+      </c>
+      <c r="B891" s="4" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>32362</v>
+      </c>
+      <c r="B892" s="5" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>32363</v>
+      </c>
+      <c r="B893" s="4" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>32364</v>
+      </c>
+      <c r="B894" s="4" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>32365</v>
+      </c>
+      <c r="B895" s="4" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>32366</v>
+      </c>
+      <c r="B896" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>32367</v>
+      </c>
+      <c r="B897" s="4" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>32368</v>
+      </c>
+      <c r="B898" s="4" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>32369</v>
+      </c>
+      <c r="B899" s="4" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>32370</v>
+      </c>
+      <c r="B900" s="2" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>32371</v>
+      </c>
+      <c r="B901" s="4" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>32372</v>
+      </c>
+      <c r="B902" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>32373</v>
+      </c>
+      <c r="B903" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>32374</v>
+      </c>
+      <c r="B904" s="4" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>32375</v>
+      </c>
+      <c r="B905" s="4" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>32376</v>
+      </c>
+      <c r="B906" s="4" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>32377</v>
+      </c>
+      <c r="B907" s="4" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>32378</v>
+      </c>
+      <c r="B908" s="2" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>32379</v>
+      </c>
+      <c r="B909" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>32380</v>
+      </c>
+      <c r="B910" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>32381</v>
+      </c>
+      <c r="B911" s="4" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>32382</v>
+      </c>
+      <c r="B912" s="4" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>32383</v>
+      </c>
+      <c r="B913" s="4" t="n">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>32384</v>
+      </c>
+      <c r="B914" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>32385</v>
+      </c>
+      <c r="B915" s="4" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>32386</v>
+      </c>
+      <c r="B916" s="2" t="n">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>32387</v>
+      </c>
+      <c r="B917" s="4" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>32388</v>
+      </c>
+      <c r="B918" s="4" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>32389</v>
+      </c>
+      <c r="B919" s="4" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>32390</v>
+      </c>
+      <c r="B920" s="4" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>32391</v>
+      </c>
+      <c r="B921" s="2" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>32392</v>
+      </c>
+      <c r="B922" s="4" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>32393</v>
+      </c>
+      <c r="B923" s="4" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>32394</v>
+      </c>
+      <c r="B924" s="4" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>32395</v>
+      </c>
+      <c r="B925" s="4" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>32396</v>
+      </c>
+      <c r="B926" s="4" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>32397</v>
+      </c>
+      <c r="B927" s="4" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>32398</v>
+      </c>
+      <c r="B928" s="4" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>32399</v>
+      </c>
+      <c r="B929" s="3" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>32400</v>
+      </c>
+      <c r="B930" s="2" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>32401</v>
+      </c>
+      <c r="B931" s="5" t="n">
+        <v>11.29</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>32402</v>
+      </c>
+      <c r="B932" s="4" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>32403</v>
+      </c>
+      <c r="B933" s="4" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>32404</v>
+      </c>
+      <c r="B934" s="4" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>32405</v>
+      </c>
+      <c r="B935" s="4" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>32406</v>
+      </c>
+      <c r="B936" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>32407</v>
+      </c>
+      <c r="B937" s="4" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>32408</v>
+      </c>
+      <c r="B938" s="4" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>32409</v>
+      </c>
+      <c r="B939" s="2" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>32410</v>
+      </c>
+      <c r="B940" s="4" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>32411</v>
+      </c>
+      <c r="B941" s="4" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>32412</v>
+      </c>
+      <c r="B942" s="4" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>32413</v>
+      </c>
+      <c r="B943" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>32414</v>
+      </c>
+      <c r="B944" s="2" t="n">
+        <v>3.26</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>32415</v>
+      </c>
+      <c r="B945" s="4" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>32416</v>
+      </c>
+      <c r="B946" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>32417</v>
+      </c>
+      <c r="B947" s="4" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>32418</v>
+      </c>
+      <c r="B948" s="4" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>32419</v>
+      </c>
+      <c r="B949" s="4" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>32420</v>
+      </c>
+      <c r="B950" s="4" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>32421</v>
+      </c>
+      <c r="B951" s="4" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>32422</v>
+      </c>
+      <c r="B952" s="4" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>32423</v>
+      </c>
+      <c r="B953" s="2" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>32424</v>
+      </c>
+      <c r="B954" s="4" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>32425</v>
+      </c>
+      <c r="B955" s="4" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>32426</v>
+      </c>
+      <c r="B956" s="4" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>32427</v>
+      </c>
+      <c r="B957" s="4" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>32428</v>
+      </c>
+      <c r="B958" s="4" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>32429</v>
+      </c>
+      <c r="B959" s="3" t="n">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>32430</v>
+      </c>
+      <c r="B960" s="4" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>32431</v>
+      </c>
+      <c r="B961" s="4" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>32432</v>
+      </c>
+      <c r="B962" s="4" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>32433</v>
+      </c>
+      <c r="B963" s="4" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>32434</v>
+      </c>
+      <c r="B964" s="4" t="n">
+        <v>1.76</v>
       </c>
     </row>
   </sheetData>
